--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1022"/>
+  <dimension ref="A1:Z1023"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43585</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>43868</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44796</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44313</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>43486</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>43633</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>43788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44920</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>43472</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44311</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44637</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>43788</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>43959</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>43472</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44070</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43398</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>43635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44232</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44523</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>43788</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>43585</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>43859</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44166</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45266</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>43472</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>43502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>43502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>43788</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44676</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45180</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>43509</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>43591</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44501</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44742</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44796</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>43472</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44319</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44634</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44641</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45146</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45308</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>43370</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>43376</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>43484</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>43504</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43543</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43691</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>43788</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>43899</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43942</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43983</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>43987</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44319</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44427</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44464</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44631</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44721</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44790</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45119</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45245</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45246</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>43318</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>43325</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43325</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43327</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43332</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>43334</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>43346</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>43347</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>43349</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>43369</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>43371</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>43375</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>43375</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>43381</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>43388</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>43389</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>43389</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>43392</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>43392</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>43392</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>43402</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>43404</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>43409</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>43409</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43409</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>43409</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>43412</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>43416</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>43424</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>43425</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>43425</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>43425</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>43426</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>43427</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>43427</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43431</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43433</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43433</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>43434</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>43437</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43443</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>43445</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>43448</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>43448</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43448</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43448</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>43448</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>43448</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43448</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43448</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>43448</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43448</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>43448</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43451</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43452</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43453</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43454</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43455</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43472</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43472</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43473</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43476</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43481</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43481</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43482</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43484</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43484</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43486</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43486</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43489</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>43489</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>43489</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>43489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>43489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>43489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>43489</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>43489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>43495</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>43504</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>43518</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>43522</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>43522</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>43523</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>43523</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>43523</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>43528</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>43529</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>43537</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>43538</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>43543</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>43549</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>43549</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>43553</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>43558</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>43563</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43565</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43565</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43587</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43590</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43595</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43609</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43610</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43610</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43614</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43614</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>43614</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>43619</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>43623</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>43631</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>43631</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>43633</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>43634</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>43634</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>43636</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>43643</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43643</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>43647</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43651</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>43654</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>43654</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>43656</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43657</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>43658</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43675</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43675</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>43677</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>43683</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>43684</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>43686</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>43686</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43690</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43700</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>43700</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>43703</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>43713</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>43713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>43713</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>43717</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>43720</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>43726</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43733</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43733</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43734</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43735</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43735</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43735</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>43749</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>43762</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>43763</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>43767</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>43782</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>43782</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>43783</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>43787</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>43788</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>43788</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>43788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>43812</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>43819</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>43837</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>43839</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>43859</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>43878</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>43878</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>43886</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>43888</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43906</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43907</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43907</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43909</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43923</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>43924</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43927</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43928</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43930</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43938</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43943</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43945</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43970</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43979</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>43986</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>43986</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>43986</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>43987</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>43990</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>43990</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>43990</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>43990</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>43990</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>43991</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>43997</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>43998</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>43999</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>43999</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>44000</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>44005</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44007</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44012</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44012</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44020</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44021</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44021</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>44043</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>44049</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>44056</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44056</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>44056</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44057</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>44061</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>44068</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>44068</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44071</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>44078</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44084</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44088</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>44090</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44090</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>44096</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>44097</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>44097</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44103</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44105</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>44110</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>44110</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>44131</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>44134</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>44137</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>44137</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>44137</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44144</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>44144</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44146</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>44148</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>44149</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44153</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>44154</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>44165</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44165</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44166</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44166</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44166</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44175</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44182</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44183</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>44185</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>44185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>44185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>44194</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44200</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44201</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>44203</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22910,7 +22910,7 @@
         <v>44208</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44210</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44211</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>44214</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>44214</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44214</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44217</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44224</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44229</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44235</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44242</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44267</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44267</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44271</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44277</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44277</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44286</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44299</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44300</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44306</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>44312</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>44313</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>44313</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44313</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>44314</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44315</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44319</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44321</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44321</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44321</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44325</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>44326</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44326</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44328</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44332</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>44332</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>44333</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>44335</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>44342</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>44347</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>44348</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>44349</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44350</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44351</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44351</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44354</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44355</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44356</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>44356</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44363</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>44363</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>44363</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>44364</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>44375</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>44375</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>44375</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44379</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44390</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>44390</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>44405</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>44405</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44405</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>44411</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44424</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44424</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44424</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>44433</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44435</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>44438</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>44438</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>44438</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>44439</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>44440</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>44442</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44445</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>44445</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>44445</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44445</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44445</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44447</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44460</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44462</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44462</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44468</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44469</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>44473</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44475</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>44477</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>44489</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>44491</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>44494</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44495</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44501</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>44501</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>44501</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>44503</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>44504</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29645,7 +29645,7 @@
         <v>44508</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>44508</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>44511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>44512</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>44512</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>44512</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>44512</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44512</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44515</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>44515</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>44516</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>44523</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>44523</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44526</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>44529</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>44531</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>44533</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44537</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>44540</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>44540</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>44544</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>44546</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>44547</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>44550</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44557</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>44582</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44588</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>44589</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>44599</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>44602</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>44603</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>44603</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44613</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>44623</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>44623</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>44631</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44637</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44641</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44643</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44644</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>44644</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>44671</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>44676</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>44677</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>44678</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>44686</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>44687</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44692</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44692</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44696</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>44697</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44701</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>44704</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44706</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44711</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>44712</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>44721</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44721</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>44721</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>44721</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>44725</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>44725</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44725</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44725</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44725</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44725</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44726</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44733</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44734</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44741</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>44741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44743</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44743</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>44743</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>44743</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44749</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>44749</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44750</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44754</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>44756</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44756</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44782</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>44789</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>44789</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44791</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>44795</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>44795</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>44796</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>44802</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>44802</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44804</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>44806</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>44809</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>44809</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>44809</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>44809</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>44810</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>44811</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>44811</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>44811</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>44811</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44811</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>44811</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>44813</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>44817</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>44819</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>44826</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44832</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>44833</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44833</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>44833</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>44834</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>44834</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>44837</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>44839</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>44840</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>44840</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>44841</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>44841</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44844</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44847</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>44852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>44853</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44853</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>44855</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44858</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>44858</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44859</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>44860</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>44862</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>44862</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>44862</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>44867</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>44867</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44869</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44875</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44882</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>44886</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>44886</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44887</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>44888</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>44890</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>44893</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44893</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>44894</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>44896</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>44897</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>44897</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>44897</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>44900</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>44900</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>44903</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>44907</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>44907</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>44908</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>44908</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>44908</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>44911</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>44916</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>44923</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>44923</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>44923</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44923</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>44923</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>44928</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>44928</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>44928</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>44931</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>44936</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>44936</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>44937</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>44938</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>44938</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>44938</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>44944</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>44944</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>44946</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>44946</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>44950</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>44957</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44963</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44970</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44978</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44978</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44978</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44978</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44979</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44981</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44991</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44994</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>45001</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45002</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>45007</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>45015</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>45015</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>45019</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>45020</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>45020</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45027</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45034</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45036</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>45036</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45036</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45037</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>45041</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45041</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45041</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45048</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45053</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>45053</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45053</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45054</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45054</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45054</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45054</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>45054</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45054</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45056</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45056</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45057</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>45057</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>45058</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>45058</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>45061</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45062</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45063</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45063</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45068</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45068</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>45071</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45071</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45072</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45072</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45072</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45072</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>45072</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45072</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45072</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45075</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>45076</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>45076</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>45077</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>45077</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>45078</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>45078</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47027,7 +47027,7 @@
         <v>45078</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>45078</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>45079</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>45079</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>45084</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47518,7 +47518,7 @@
         <v>45084</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>45084</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47637,7 +47637,7 @@
         <v>45086</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45086</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>45089</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47818,7 +47818,7 @@
         <v>45089</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45089</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>45089</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47994,7 +47994,7 @@
         <v>45089</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45090</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>45090</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48175,7 +48175,7 @@
         <v>45090</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>45090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>45090</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>45090</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45092</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>45092</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>45093</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45093</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45096</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45096</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45097</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45097</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45097</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45099</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>45099</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45103</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>45104</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49221,7 +49221,7 @@
         <v>45106</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45106</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45106</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45106</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>45106</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45110</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>45112</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45114</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50116,7 +50116,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45118</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>45118</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50344,7 +50344,7 @@
         <v>45118</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>45119</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>45121</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45121</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45128</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45128</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50706,7 +50706,7 @@
         <v>45128</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50768,7 +50768,7 @@
         <v>45128</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45128</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45128</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45134</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51016,7 +51016,7 @@
         <v>45139</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>45139</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51130,7 +51130,7 @@
         <v>45146</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>45149</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45152</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45152</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>45153</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>45160</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45160</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45162</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>45162</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>45163</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45167</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52092,7 +52092,7 @@
         <v>45168</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>45169</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52273,7 +52273,7 @@
         <v>45169</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>45170</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45170</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45170</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52521,7 +52521,7 @@
         <v>45173</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>45173</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52635,7 +52635,7 @@
         <v>45173</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>45173</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45173</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45175</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>45175</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>45175</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52977,7 +52977,7 @@
         <v>45175</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         <v>45176</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53153,7 +53153,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45181</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45187</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45187</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45187</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>45187</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         <v>45187</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53567,7 +53567,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53681,7 +53681,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53738,7 +53738,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53795,7 +53795,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53852,7 +53852,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53909,7 +53909,7 @@
         <v>45190</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53966,7 +53966,7 @@
         <v>45190</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54023,7 +54023,7 @@
         <v>45190</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54147,7 +54147,7 @@
         <v>45191</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54204,7 +54204,7 @@
         <v>45191</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54261,7 +54261,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54375,7 +54375,7 @@
         <v>45195</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54432,7 +54432,7 @@
         <v>45195</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54489,7 +54489,7 @@
         <v>45195</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45195</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45197</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45197</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45198</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54784,7 +54784,7 @@
         <v>45198</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45198</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45198</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54970,7 +54970,7 @@
         <v>45201</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>45201</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
         <v>45202</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>45202</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55198,7 +55198,7 @@
         <v>45203</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45203</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55312,7 +55312,7 @@
         <v>45204</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55374,7 +55374,7 @@
         <v>45204</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>45204</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55498,7 +55498,7 @@
         <v>45204</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>45204</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>45205</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55679,7 +55679,7 @@
         <v>45205</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55793,7 +55793,7 @@
         <v>45211</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>45215</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55907,7 +55907,7 @@
         <v>45215</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55969,7 +55969,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>45219</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>45219</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>45219</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>45219</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56254,7 +56254,7 @@
         <v>45220</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56311,7 +56311,7 @@
         <v>45223</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56373,7 +56373,7 @@
         <v>45223</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56430,7 +56430,7 @@
         <v>45223</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>45223</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>45224</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56611,7 +56611,7 @@
         <v>45225</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56668,7 +56668,7 @@
         <v>45225</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56725,7 +56725,7 @@
         <v>45225</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56787,7 +56787,7 @@
         <v>45225</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56849,7 +56849,7 @@
         <v>45225</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56911,7 +56911,7 @@
         <v>45225</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45225</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57030,7 +57030,7 @@
         <v>45225</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>45225</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>45225</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57206,7 +57206,7 @@
         <v>45226</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57263,7 +57263,7 @@
         <v>45226</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57320,7 +57320,7 @@
         <v>45226</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57377,7 +57377,7 @@
         <v>45226</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57434,7 +57434,7 @@
         <v>45226</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57491,7 +57491,7 @@
         <v>45226</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>45229</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57615,7 +57615,7 @@
         <v>45229</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>45229</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>45231</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>45231</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57858,7 +57858,7 @@
         <v>45231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57920,7 +57920,7 @@
         <v>45231</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57977,7 +57977,7 @@
         <v>45233</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>45236</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45236</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>45236</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58210,7 +58210,7 @@
         <v>45237</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58267,7 +58267,7 @@
         <v>45237</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58324,7 +58324,7 @@
         <v>45237</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>45237</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45237</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58495,7 +58495,7 @@
         <v>45238</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>45238</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58609,7 +58609,7 @@
         <v>45238</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         <v>45243</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58780,7 +58780,7 @@
         <v>45243</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58837,7 +58837,7 @@
         <v>45243</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58894,7 +58894,7 @@
         <v>45243</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58951,7 +58951,7 @@
         <v>45243</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>45243</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>45244</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59122,7 +59122,7 @@
         <v>45244</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>45245</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59236,7 +59236,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59293,7 +59293,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59350,7 +59350,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59407,7 +59407,7 @@
         <v>45246</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59464,7 +59464,7 @@
         <v>45247</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59526,7 +59526,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59588,7 +59588,7 @@
         <v>45247</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59645,7 +59645,7 @@
         <v>45252</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59702,7 +59702,7 @@
         <v>45252</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>45252</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59816,7 +59816,7 @@
         <v>45252</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59930,7 +59930,7 @@
         <v>45253</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59992,7 +59992,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60054,7 +60054,7 @@
         <v>45254</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60116,7 +60116,7 @@
         <v>45257</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60173,7 +60173,7 @@
         <v>45257</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60235,7 +60235,7 @@
         <v>45257</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60292,7 +60292,7 @@
         <v>45257</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60354,7 +60354,7 @@
         <v>45260</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60411,7 +60411,7 @@
         <v>45260</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60468,7 +60468,7 @@
         <v>45260</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60525,7 +60525,7 @@
         <v>45264</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60582,7 +60582,7 @@
         <v>45266</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60639,7 +60639,7 @@
         <v>45266</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60696,7 +60696,7 @@
         <v>45266</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60753,7 +60753,7 @@
         <v>45267</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>45270</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60867,7 +60867,7 @@
         <v>45271</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60924,7 +60924,7 @@
         <v>45271</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60981,7 +60981,7 @@
         <v>45272</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61038,7 +61038,7 @@
         <v>45273</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61095,7 +61095,7 @@
         <v>45280</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61152,7 +61152,7 @@
         <v>45293</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61209,7 +61209,7 @@
         <v>45294</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61266,7 +61266,7 @@
         <v>45294</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
         <v>45299</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61380,7 +61380,7 @@
         <v>45301</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45301</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61494,7 +61494,7 @@
         <v>45301</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61551,7 +61551,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61608,7 +61608,7 @@
         <v>45301</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61665,7 +61665,7 @@
         <v>45302</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61727,7 +61727,7 @@
         <v>45302</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61789,7 +61789,7 @@
         <v>45303</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61846,7 +61846,7 @@
         <v>45308</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61903,7 +61903,7 @@
         <v>45308</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61965,7 +61965,7 @@
         <v>45313</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62022,7 +62022,7 @@
         <v>45314</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62079,7 +62079,7 @@
         <v>45315</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62129,14 +62129,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 3789-2024</t>
+          <t>A 3792-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -62191,14 +62191,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 3794-2024</t>
+          <t>A 3789-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62216,7 +62216,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -62253,14 +62253,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 3792-2024</t>
+          <t>A 3794-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62278,7 +62278,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -62322,7 +62322,7 @@
         <v>45322</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45322</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62436,7 +62436,7 @@
         <v>45324</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62493,7 +62493,7 @@
         <v>45334</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
       </c>
       <c r="R1021" s="2" t="inlineStr"/>
     </row>
-    <row r="1022">
+    <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
           <t>A 5577-2024</t>
@@ -62550,7 +62550,7 @@
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62596,6 +62596,63 @@
         <v>0</v>
       </c>
       <c r="R1022" s="2" t="inlineStr"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>A 5992-2024</t>
+        </is>
+      </c>
+      <c r="B1023" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="C1023" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>MALUNG-SÄLEN</t>
+        </is>
+      </c>
+      <c r="G1023" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1023" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1023"/>
+  <dimension ref="A1:Z1025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43585</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>43868</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44796</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44313</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>43486</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>43633</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>43788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44920</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>43472</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44311</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44637</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>43788</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>43959</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>43472</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44070</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43398</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>43635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44232</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44523</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>43788</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>43585</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>43859</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44166</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45266</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>43472</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>43502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>43502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>43788</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44676</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45180</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>43509</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>43591</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44501</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44742</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44796</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>43472</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44319</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44634</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44641</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45146</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45308</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>43370</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>43376</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>43484</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>43504</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43543</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43691</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>43788</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>43899</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43942</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43983</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>43987</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44319</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44427</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44464</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44631</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44721</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44790</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45119</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45245</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45246</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>43318</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>43325</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43325</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>43327</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>43332</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>43334</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>43346</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>43347</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>43349</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>43369</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>43371</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>43375</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>43375</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>43381</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>43388</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>43389</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>43389</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>43392</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>43392</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>43392</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>43402</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>43404</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>43409</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>43409</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43409</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>43409</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>43412</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>43416</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>43424</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>43425</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>43425</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>43425</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>43426</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>43427</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>43427</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43431</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43433</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>43433</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>43434</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>43437</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43443</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>43445</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>43448</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>43448</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>43448</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>43448</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>43448</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>43448</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43448</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>43448</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>43448</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43448</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>43448</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43451</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43452</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43453</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43454</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43455</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43472</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43472</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43473</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43476</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43481</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43481</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43482</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43484</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43484</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43486</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43486</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43489</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>43489</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>43489</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>43489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>43489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>43489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>43489</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>43489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>43495</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>43504</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>43518</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>43522</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>43522</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>43523</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>43523</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>43523</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>43528</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>43529</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>43537</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>43538</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>43543</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>43549</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>43549</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>43553</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>43558</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>43563</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>43565</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>43565</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>43587</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43590</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43595</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43609</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43610</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43610</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43614</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43614</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>43614</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>43619</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>43623</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>43631</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>43631</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>43633</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>43634</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>43634</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>43636</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>43643</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43643</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>43647</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43651</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>43654</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>43654</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>43656</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43657</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>43658</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43675</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43675</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>43677</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>43683</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>43684</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>43686</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>43686</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43690</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43700</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>43700</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>43703</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>43713</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>43713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>43713</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>43717</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>43720</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>43726</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43733</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43733</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43734</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43735</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43735</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43735</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>43749</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>43762</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>43763</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>43767</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>43782</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>43782</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>43783</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>43787</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>43788</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>43788</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>43788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>43812</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>43819</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>43837</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>43839</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>43859</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>43878</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>43878</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>43886</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>43888</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43906</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43907</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43907</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43909</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43923</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>43924</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43927</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43928</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43930</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43938</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43943</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43945</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43970</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43979</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>43986</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>43986</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>43986</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>43987</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>43990</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>43990</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>43990</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>43990</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>43990</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>43991</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>43997</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>43998</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>43999</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>43999</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>44000</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>44005</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44007</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44012</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44012</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44020</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44021</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44021</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>44043</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>44049</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>44056</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44056</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>44056</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44057</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>44061</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>44068</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>44068</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44071</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>44078</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44084</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44088</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>44090</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44090</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>44096</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>44097</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>44097</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>44099</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44103</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44105</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>44110</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>44110</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44111</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>44131</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>44134</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>44137</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>44137</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>44137</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44144</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>44144</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44146</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>44148</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>44149</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44153</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>44154</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>44165</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44165</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44166</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44166</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44166</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44175</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44182</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44183</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>44185</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>44185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>44185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>44194</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44200</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44201</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>44203</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22910,7 +22910,7 @@
         <v>44208</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44210</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44211</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>44214</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>44214</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44214</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44217</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44224</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44229</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44235</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44242</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44267</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>44267</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44271</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44277</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44277</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44286</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44299</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44300</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44306</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>44312</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>44313</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>44313</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44313</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>44314</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44315</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44319</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44321</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44321</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44321</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44325</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>44326</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>44326</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>44328</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>44332</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>44332</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>44333</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>44335</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>44342</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>44347</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>44348</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>44349</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44350</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44351</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44351</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44354</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44355</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44356</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>44356</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44363</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>44363</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>44363</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>44364</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>44375</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>44375</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>44375</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44379</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44390</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>44390</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>44405</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>44405</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44405</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>44411</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44424</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44424</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44424</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>44433</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44435</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>44438</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>44438</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>44438</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>44439</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>44440</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>44442</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44445</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>44445</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>44445</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44445</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44445</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44447</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44460</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44462</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44462</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44468</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44469</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>44473</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44475</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>44477</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>44489</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>44491</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>44494</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44495</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44501</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>44501</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>44501</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>44503</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>44504</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29645,7 +29645,7 @@
         <v>44508</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>44508</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>44511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>44512</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>44512</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>44512</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>44512</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44512</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44515</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>44515</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>44516</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>44523</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>44523</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44526</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>44529</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>44531</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>44533</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44537</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>44540</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>44540</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>44544</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>44546</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>44547</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>44550</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44557</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>44582</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44588</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>44589</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>44599</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>44602</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>44603</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>44603</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44613</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>44623</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>44623</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>44631</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44637</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44641</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44643</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44644</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>44644</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>44671</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>44676</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>44677</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>44678</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>44686</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>44687</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44692</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44692</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44696</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>44697</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44701</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>44704</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44706</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44711</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>44712</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>44721</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44721</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>44721</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>44721</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>44725</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>44725</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44725</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44725</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44725</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44725</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44726</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44733</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44734</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44741</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>44741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44743</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44743</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>44743</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>44743</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44749</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>44749</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44750</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44754</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>44756</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44756</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44782</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>44789</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>44789</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44791</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>44795</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>44795</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>44796</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>44802</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>44802</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44804</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>44806</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>44809</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>44809</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>44809</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>44809</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>44810</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>44811</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>44811</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>44811</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>44811</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44811</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>44811</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>44813</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>44817</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>44819</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>44826</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44832</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>44833</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44833</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>44833</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>44834</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>44834</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>44837</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>44839</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>44840</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>44840</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>44841</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>44841</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44844</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44847</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>44852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>44853</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>44853</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>44855</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44858</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>44858</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44859</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>44860</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>44862</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>44862</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>44862</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>44867</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>44867</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44869</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44875</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44881</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44882</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>44886</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>44886</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44887</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>44888</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>44890</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>44893</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44893</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>44894</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>44896</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>44897</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>44897</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>44897</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>44900</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>44900</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>44903</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>44907</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>44907</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>44908</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>44908</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>44908</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>44911</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>44916</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>44923</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>44923</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>44923</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44923</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>44923</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>44928</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>44928</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>44928</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>44931</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>44936</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>44936</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>44937</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>44938</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>44938</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>44938</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>44944</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>44944</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>44946</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>44946</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>44950</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>44957</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44963</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44970</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44978</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44978</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44978</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44978</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44979</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44981</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44991</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44994</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>45001</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45002</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>45007</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>45015</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>45015</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>45019</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>45020</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>45020</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45027</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45034</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45036</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>45036</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45036</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45037</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>45041</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45041</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45041</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45048</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45053</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>45053</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45053</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45054</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45054</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45054</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45054</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>45054</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45054</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45056</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45056</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45057</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>45057</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>45058</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>45058</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>45061</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45062</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45063</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45063</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45068</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45068</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>45071</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45071</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>45072</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45072</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45072</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45072</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>45072</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45072</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45072</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45075</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>45076</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>45076</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>45077</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>45077</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>45078</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>45078</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47027,7 +47027,7 @@
         <v>45078</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>45078</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>45079</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>45079</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>45084</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47518,7 +47518,7 @@
         <v>45084</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>45084</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47637,7 +47637,7 @@
         <v>45086</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45086</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>45089</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47818,7 +47818,7 @@
         <v>45089</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45089</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>45089</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47994,7 +47994,7 @@
         <v>45089</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45090</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>45090</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48175,7 +48175,7 @@
         <v>45090</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>45090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>45090</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>45090</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45092</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>45092</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>45093</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45093</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45096</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45096</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45097</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45097</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45097</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45099</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>45099</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45103</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>45104</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49221,7 +49221,7 @@
         <v>45106</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45106</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45106</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45106</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>45106</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45110</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>45112</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45114</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50116,7 +50116,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45118</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>45118</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50344,7 +50344,7 @@
         <v>45118</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>45119</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>45121</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45121</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45128</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45128</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50706,7 +50706,7 @@
         <v>45128</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50768,7 +50768,7 @@
         <v>45128</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45128</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45128</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45134</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51016,7 +51016,7 @@
         <v>45139</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>45139</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51130,7 +51130,7 @@
         <v>45146</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>45149</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45152</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45152</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>45153</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>45160</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45160</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45162</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>45162</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>45163</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45167</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52092,7 +52092,7 @@
         <v>45168</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>45169</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52273,7 +52273,7 @@
         <v>45169</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>45170</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45170</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45170</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52521,7 +52521,7 @@
         <v>45173</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>45173</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52635,7 +52635,7 @@
         <v>45173</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>45173</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45173</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45175</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>45175</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>45175</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52977,7 +52977,7 @@
         <v>45175</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         <v>45176</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53153,7 +53153,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45181</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45187</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45187</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45187</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>45187</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         <v>45187</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53567,7 +53567,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53681,7 +53681,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53738,7 +53738,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53795,7 +53795,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53852,7 +53852,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53909,7 +53909,7 @@
         <v>45190</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53966,7 +53966,7 @@
         <v>45190</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54023,7 +54023,7 @@
         <v>45190</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54147,7 +54147,7 @@
         <v>45191</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54204,7 +54204,7 @@
         <v>45191</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54261,7 +54261,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54375,7 +54375,7 @@
         <v>45195</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54432,7 +54432,7 @@
         <v>45195</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54489,7 +54489,7 @@
         <v>45195</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45195</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45197</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45197</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45198</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54784,7 +54784,7 @@
         <v>45198</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45198</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45198</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54970,7 +54970,7 @@
         <v>45201</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>45201</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
         <v>45202</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>45202</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55198,7 +55198,7 @@
         <v>45203</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45203</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55312,7 +55312,7 @@
         <v>45204</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55374,7 +55374,7 @@
         <v>45204</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>45204</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55498,7 +55498,7 @@
         <v>45204</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>45204</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>45205</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55679,7 +55679,7 @@
         <v>45205</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55793,7 +55793,7 @@
         <v>45211</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>45215</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55907,7 +55907,7 @@
         <v>45215</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55969,7 +55969,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>45219</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>45219</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>45219</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>45219</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56254,7 +56254,7 @@
         <v>45220</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56311,7 +56311,7 @@
         <v>45223</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56373,7 +56373,7 @@
         <v>45223</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56430,7 +56430,7 @@
         <v>45223</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>45223</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>45224</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56611,7 +56611,7 @@
         <v>45225</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56668,7 +56668,7 @@
         <v>45225</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56725,7 +56725,7 @@
         <v>45225</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56787,7 +56787,7 @@
         <v>45225</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56849,7 +56849,7 @@
         <v>45225</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56911,7 +56911,7 @@
         <v>45225</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45225</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57030,7 +57030,7 @@
         <v>45225</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>45225</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>45225</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57206,7 +57206,7 @@
         <v>45226</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57263,7 +57263,7 @@
         <v>45226</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57320,7 +57320,7 @@
         <v>45226</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57377,7 +57377,7 @@
         <v>45226</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57434,7 +57434,7 @@
         <v>45226</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57491,7 +57491,7 @@
         <v>45226</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>45229</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57615,7 +57615,7 @@
         <v>45229</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>45229</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>45231</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>45231</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57858,7 +57858,7 @@
         <v>45231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57920,7 +57920,7 @@
         <v>45231</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57977,7 +57977,7 @@
         <v>45233</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>45236</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45236</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>45236</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58210,7 +58210,7 @@
         <v>45237</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58267,7 +58267,7 @@
         <v>45237</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58324,7 +58324,7 @@
         <v>45237</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>45237</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45237</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58495,7 +58495,7 @@
         <v>45238</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>45238</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58609,7 +58609,7 @@
         <v>45238</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         <v>45243</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58780,7 +58780,7 @@
         <v>45243</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58837,7 +58837,7 @@
         <v>45243</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58894,7 +58894,7 @@
         <v>45243</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58951,7 +58951,7 @@
         <v>45243</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>45243</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>45244</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59122,7 +59122,7 @@
         <v>45244</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>45245</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59236,7 +59236,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59293,7 +59293,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59350,7 +59350,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59407,7 +59407,7 @@
         <v>45246</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59464,7 +59464,7 @@
         <v>45247</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59526,7 +59526,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59588,7 +59588,7 @@
         <v>45247</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59645,7 +59645,7 @@
         <v>45252</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59702,7 +59702,7 @@
         <v>45252</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>45252</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59816,7 +59816,7 @@
         <v>45252</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59930,7 +59930,7 @@
         <v>45253</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59992,7 +59992,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60054,7 +60054,7 @@
         <v>45254</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60116,7 +60116,7 @@
         <v>45257</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60173,7 +60173,7 @@
         <v>45257</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60235,7 +60235,7 @@
         <v>45257</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60292,7 +60292,7 @@
         <v>45257</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60354,7 +60354,7 @@
         <v>45260</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60411,7 +60411,7 @@
         <v>45260</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60468,7 +60468,7 @@
         <v>45260</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60525,7 +60525,7 @@
         <v>45264</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60582,7 +60582,7 @@
         <v>45266</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60639,7 +60639,7 @@
         <v>45266</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60696,7 +60696,7 @@
         <v>45266</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60753,7 +60753,7 @@
         <v>45267</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>45270</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60867,7 +60867,7 @@
         <v>45271</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60924,7 +60924,7 @@
         <v>45271</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60981,7 +60981,7 @@
         <v>45272</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61038,7 +61038,7 @@
         <v>45273</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61095,7 +61095,7 @@
         <v>45280</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61152,7 +61152,7 @@
         <v>45293</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61209,7 +61209,7 @@
         <v>45294</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61266,7 +61266,7 @@
         <v>45294</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
         <v>45299</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61380,7 +61380,7 @@
         <v>45301</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45301</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61494,7 +61494,7 @@
         <v>45301</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61551,7 +61551,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61608,7 +61608,7 @@
         <v>45301</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61665,7 +61665,7 @@
         <v>45302</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61727,7 +61727,7 @@
         <v>45302</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61789,7 +61789,7 @@
         <v>45303</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61846,7 +61846,7 @@
         <v>45308</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61903,7 +61903,7 @@
         <v>45308</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61965,7 +61965,7 @@
         <v>45313</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62022,7 +62022,7 @@
         <v>45314</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62079,7 +62079,7 @@
         <v>45315</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62136,7 +62136,7 @@
         <v>45321</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62198,7 +62198,7 @@
         <v>45321</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62260,7 +62260,7 @@
         <v>45321</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62322,7 +62322,7 @@
         <v>45322</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45322</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62436,7 +62436,7 @@
         <v>45324</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62493,7 +62493,7 @@
         <v>45334</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62550,7 +62550,7 @@
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
       </c>
       <c r="R1022" s="2" t="inlineStr"/>
     </row>
-    <row r="1023">
+    <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
           <t>A 5992-2024</t>
@@ -62607,7 +62607,7 @@
         <v>45336</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62653,6 +62653,125 @@
         <v>0</v>
       </c>
       <c r="R1023" s="2" t="inlineStr"/>
+    </row>
+    <row r="1024" ht="15" customHeight="1">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>A 6407-2024</t>
+        </is>
+      </c>
+      <c r="B1024" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C1024" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>MALUNG-SÄLEN</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="G1024" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1024" s="2" t="inlineStr"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>A 6496-2024</t>
+        </is>
+      </c>
+      <c r="B1025" s="1" t="n">
+        <v>45339</v>
+      </c>
+      <c r="C1025" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>MALUNG-SÄLEN</t>
+        </is>
+      </c>
+      <c r="G1025" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1025" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43585</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>43868</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44796</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44313</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>43486</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>43633</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>43788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44920</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>43472</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44311</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44637</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>43788</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>43959</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>43472</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44070</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43398</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>43635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44232</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44523</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>43788</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>43585</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>43859</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44166</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45266</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>43472</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>43502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>43502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>43788</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44676</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45180</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>43509</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>43591</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44501</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44742</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44796</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>43472</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44319</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44634</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44641</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45146</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45308</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>43370</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>43376</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>43484</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>43504</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43543</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43691</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>43788</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>43899</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43942</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43983</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>43987</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44319</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44427</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44464</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44631</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44721</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44790</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45119</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45245</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45246</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6550,14 +6550,14 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6807-2024</t>
+          <t>A 6806-2024</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6608,115 +6608,115 @@
         </is>
       </c>
       <c r="S68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2023/artfynd/A 6806-2024 artfynd.xlsx", "A 6806-2024")</f>
+        <v/>
+      </c>
+      <c r="T68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2023/kartor/A 6806-2024 karta.png", "A 6806-2024")</f>
+        <v/>
+      </c>
+      <c r="V68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2023/klagomål/A 6806-2024 FSC-klagomål.docx", "A 6806-2024")</f>
+        <v/>
+      </c>
+      <c r="W68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2023/klagomålsmail/A 6806-2024 FSC-klagomål mail.docx", "A 6806-2024")</f>
+        <v/>
+      </c>
+      <c r="X68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2023/tillsyn/A 6806-2024 tillsynsbegäran.docx", "A 6806-2024")</f>
+        <v/>
+      </c>
+      <c r="Y68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2023/tillsynsmail/A 6806-2024 tillsynsbegäran mail.docx", "A 6806-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A 6807-2024</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>MALUNG-SÄLEN</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="S69">
         <f>HYPERLINK("https://klasma.github.io/Logging_2023/artfynd/A 6807-2024 artfynd.xlsx", "A 6807-2024")</f>
         <v/>
       </c>
-      <c r="T68">
+      <c r="T69">
         <f>HYPERLINK("https://klasma.github.io/Logging_2023/kartor/A 6807-2024 karta.png", "A 6807-2024")</f>
         <v/>
       </c>
-      <c r="V68">
+      <c r="V69">
         <f>HYPERLINK("https://klasma.github.io/Logging_2023/klagomål/A 6807-2024 FSC-klagomål.docx", "A 6807-2024")</f>
         <v/>
       </c>
-      <c r="W68">
+      <c r="W69">
         <f>HYPERLINK("https://klasma.github.io/Logging_2023/klagomålsmail/A 6807-2024 FSC-klagomål mail.docx", "A 6807-2024")</f>
         <v/>
       </c>
-      <c r="X68">
+      <c r="X69">
         <f>HYPERLINK("https://klasma.github.io/Logging_2023/tillsyn/A 6807-2024 tillsynsbegäran.docx", "A 6807-2024")</f>
         <v/>
       </c>
-      <c r="Y68">
+      <c r="Y69">
         <f>HYPERLINK("https://klasma.github.io/Logging_2023/tillsynsmail/A 6807-2024 tillsynsbegäran mail.docx", "A 6807-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>A 6806-2024</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="n">
-        <v>45342</v>
-      </c>
-      <c r="C69" s="1" t="n">
-        <v>45343</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>MALUNG-SÄLEN</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>1</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1</v>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="S69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2023/artfynd/A 6806-2024 artfynd.xlsx", "A 6806-2024")</f>
-        <v/>
-      </c>
-      <c r="T69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2023/kartor/A 6806-2024 karta.png", "A 6806-2024")</f>
-        <v/>
-      </c>
-      <c r="V69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2023/klagomål/A 6806-2024 FSC-klagomål.docx", "A 6806-2024")</f>
-        <v/>
-      </c>
-      <c r="W69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2023/klagomålsmail/A 6806-2024 FSC-klagomål mail.docx", "A 6806-2024")</f>
-        <v/>
-      </c>
-      <c r="X69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2023/tillsyn/A 6806-2024 tillsynsbegäran.docx", "A 6806-2024")</f>
-        <v/>
-      </c>
-      <c r="Y69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2023/tillsynsmail/A 6806-2024 tillsynsbegäran mail.docx", "A 6806-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>43318</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>43325</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>43325</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>43327</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>43332</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>43334</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43346</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>43347</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>43349</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>43369</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>43371</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>43375</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>43375</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>43381</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>43388</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>43388</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>43389</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>43389</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>43392</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>43392</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>43392</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>43402</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>43404</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>43409</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>43409</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>43409</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>43409</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>43412</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>43416</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>43424</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>43425</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>43425</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>43425</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>43426</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>43427</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>43427</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>43431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>43431</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>43433</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>43433</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>43433</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>43434</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>43437</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>43438</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>43440</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43443</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>43444</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43445</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43448</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>43448</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>43448</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>43448</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>43448</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>43448</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>43448</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>43448</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>43448</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>43451</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>43452</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>43453</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>43454</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>43455</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>43472</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>43472</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>43473</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>43476</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>43481</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>43481</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>43482</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>43482</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>43484</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>43484</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>43486</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>43486</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>43489</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>43489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>43489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>43489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>43489</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>43489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>43489</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>43489</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43495</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43504</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43518</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>43522</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>43522</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>43523</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>43523</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43523</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>43528</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43529</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43537</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>43538</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>43543</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>43549</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43549</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43553</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43558</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>43563</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>43565</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>43565</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>43587</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43590</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43595</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43609</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>43610</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43610</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43614</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43614</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43614</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43619</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43623</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43631</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>43631</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>43633</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>43634</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>43634</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>43636</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>43643</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>43643</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>43647</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>43651</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>43654</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>43656</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>43657</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>43658</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>43675</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>43675</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43677</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43683</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43684</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43686</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>43686</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>43690</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>43700</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>43700</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>43703</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>43713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>43713</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>43713</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>43713</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>43717</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>43720</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>43726</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>43733</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>43733</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>43734</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>43735</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>43735</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>43735</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>43735</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>43739</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>43747</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>43749</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>43762</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>43763</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>43767</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>43782</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>43782</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>43783</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>43787</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>43788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>43788</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>43788</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>43812</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>43819</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>43837</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>43839</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>43859</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>43878</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>43886</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>43888</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>43894</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>43906</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>43907</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>43907</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>43909</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>43923</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>43924</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>43927</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>43928</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>43930</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>43938</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>43943</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>43945</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>43970</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>43979</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>43986</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>43986</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>43986</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>43987</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>43990</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>43990</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>43990</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>43990</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>43990</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>43991</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>43997</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>43998</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>43999</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>43999</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>44000</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>44005</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>44007</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44012</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44012</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44020</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44021</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>44021</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>44043</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>44049</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44056</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44056</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>44056</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44057</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>44061</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44068</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44068</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44071</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44078</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44084</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44088</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44090</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>44090</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>44096</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>44097</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>44097</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44099</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>44103</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>44105</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>44110</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44110</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44111</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44131</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44131</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44134</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>44137</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>44137</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>44137</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>44144</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44144</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>44146</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>44148</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>44149</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>44153</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>44154</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>44165</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>44165</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44166</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44166</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>44166</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>44175</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>44182</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>44183</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>44185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>44185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>44185</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44194</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>44200</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>44201</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>44203</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>44208</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>44210</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>44211</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>44214</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>44214</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>44214</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>44217</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>44222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>44224</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>44229</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>44235</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>44242</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44267</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>44267</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>44271</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>44277</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>44277</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>44286</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>44299</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>44300</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>44306</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44312</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44313</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44313</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44313</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44314</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>44315</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44319</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44319</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44321</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44321</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44321</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44325</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44326</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>44326</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44328</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44332</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>44332</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>44333</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>44335</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>44342</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>44347</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>44348</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>44349</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>44350</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>44351</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44351</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>44351</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>44354</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>44355</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>44356</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>44356</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>44363</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>44363</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44363</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>44364</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>44375</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>44375</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44375</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>44379</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>44384</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44385</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44390</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44390</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>44405</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44405</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44405</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44411</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>44419</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>44424</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>44424</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>44424</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>44426</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>44433</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>44435</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44438</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>44438</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>44438</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>44439</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44440</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>44440</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>44442</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>44445</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44445</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44445</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44447</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44460</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44462</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44462</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44462</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44468</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44469</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44473</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44475</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44489</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44491</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>44494</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>44495</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>44497</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>44501</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44501</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>44501</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44501</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44503</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44504</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44508</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44508</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>44511</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>44511</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44512</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>44512</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44512</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44512</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44512</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44515</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44516</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>44523</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>44523</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>44526</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44529</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44531</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>44533</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>44537</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>44540</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>44540</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>44544</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>44546</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>44547</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>44550</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>44552</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>44557</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>44582</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>44589</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>44599</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>44600</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>44603</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>44603</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>44610</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>44613</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>44616</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44616</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44623</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44623</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44631</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44637</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44643</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44644</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44644</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>44671</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44676</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32884,7 +32884,7 @@
         <v>44677</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44678</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>44686</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44687</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>44692</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44692</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>44696</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>44701</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44704</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44706</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44721</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>44721</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>44721</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44721</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>44725</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44725</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>44725</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>44725</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>44725</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44725</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>44726</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>44733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44733</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44733</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44734</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44739</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44743</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>44743</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>44743</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>44743</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44749</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>44750</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>44754</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>44756</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>44756</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>44782</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>44789</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>44789</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>44791</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>44795</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>44795</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>44796</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>44797</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>44802</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>44802</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>44804</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>44806</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>44809</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>44809</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>44809</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>44810</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>44811</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>44811</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>44811</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>44811</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>44811</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>44811</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>44813</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>44817</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>44819</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>44826</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>44832</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44832</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>44833</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>44833</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>44833</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37483,7 +37483,7 @@
         <v>44834</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37540,7 +37540,7 @@
         <v>44834</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>44837</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>44840</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>44840</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>44841</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>44841</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>44844</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>44847</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>44851</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>44852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>44853</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>44853</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>44855</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44858</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>44859</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>44860</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>44862</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38844,7 +38844,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44862</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44862</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>44865</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44867</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44867</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>44868</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44869</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44875</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44881</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44882</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>44886</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39947,7 +39947,7 @@
         <v>44887</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44888</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44888</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44890</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>44893</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>44894</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44896</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>44897</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44897</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44897</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44900</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>44900</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>44903</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>44907</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>44908</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>44908</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>44910</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>44911</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>44914</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>44916</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>44923</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>44923</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>44923</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>44923</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>44923</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44928</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44928</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>44928</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44931</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>44936</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>44936</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>44937</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>44938</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>44938</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44938</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44944</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>44946</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>44946</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>44950</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>44950</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44957</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>44963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>44963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>44963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>44970</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>44978</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>44978</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>44978</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>44978</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43459,7 +43459,7 @@
         <v>44979</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43516,7 +43516,7 @@
         <v>44981</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>44991</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>44994</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45001</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45002</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45007</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45015</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45015</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45019</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>45020</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45020</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
         <v>45027</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44324,7 +44324,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>45034</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45036</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>45036</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>45036</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>45036</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44666,7 +44666,7 @@
         <v>45037</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45041</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>45041</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45041</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45048</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45053</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45053</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45053</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45054</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45054</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45054</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>45054</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45054</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45054</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45056</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45056</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45057</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45057</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>45058</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45058</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45061</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45062</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45960,7 +45960,7 @@
         <v>45063</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45063</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>45068</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>45068</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46188,7 +46188,7 @@
         <v>45071</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45071</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46312,7 +46312,7 @@
         <v>45072</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45072</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>45072</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45072</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>45072</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45072</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>45072</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>45075</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45076</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45076</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>45077</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45077</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45078</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45078</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45078</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>45078</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47383,7 +47383,7 @@
         <v>45079</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47445,7 +47445,7 @@
         <v>45079</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47502,7 +47502,7 @@
         <v>45079</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>45079</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>45084</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45084</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45084</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45086</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>45086</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47931,7 +47931,7 @@
         <v>45089</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47988,7 +47988,7 @@
         <v>45089</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48045,7 +48045,7 @@
         <v>45089</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>45089</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>45089</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48226,7 +48226,7 @@
         <v>45090</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48288,7 +48288,7 @@
         <v>45090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>45090</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>45090</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>45090</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>45090</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48573,7 +48573,7 @@
         <v>45092</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>45092</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>45093</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48749,7 +48749,7 @@
         <v>45093</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>45096</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48863,7 +48863,7 @@
         <v>45096</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45097</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>45097</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45097</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>45099</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45099</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45103</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45104</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45106</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45106</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49510,7 +49510,7 @@
         <v>45106</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45106</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45106</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45107</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45110</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45110</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49929,7 +49929,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50053,7 +50053,7 @@
         <v>45112</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50172,7 +50172,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50229,7 +50229,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45114</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50400,7 +50400,7 @@
         <v>45118</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50514,7 +50514,7 @@
         <v>45118</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>45119</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>45121</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50690,7 +50690,7 @@
         <v>45121</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>45128</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50814,7 +50814,7 @@
         <v>45128</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50876,7 +50876,7 @@
         <v>45128</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>45128</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45128</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>45128</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>45134</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>45139</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45139</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45146</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>45149</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>45152</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45152</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>45153</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>45160</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>45160</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51714,7 +51714,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45162</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>45162</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45163</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>45163</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45163</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>45167</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52143,7 +52143,7 @@
         <v>45168</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52200,7 +52200,7 @@
         <v>45168</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>45168</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>45169</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>45169</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52443,7 +52443,7 @@
         <v>45169</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>45170</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>45170</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>45170</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52691,7 +52691,7 @@
         <v>45173</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52748,7 +52748,7 @@
         <v>45173</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52805,7 +52805,7 @@
         <v>45173</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45173</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52919,7 +52919,7 @@
         <v>45173</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52976,7 +52976,7 @@
         <v>45175</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53033,7 +53033,7 @@
         <v>45175</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53090,7 +53090,7 @@
         <v>45175</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>45175</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53204,7 +53204,7 @@
         <v>45176</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53323,7 +53323,7 @@
         <v>45177</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53380,7 +53380,7 @@
         <v>45181</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>45187</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45187</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53566,7 +53566,7 @@
         <v>45187</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>45187</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45187</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45190</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45190</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45190</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45190</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45191</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45191</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45194</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45195</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45195</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45195</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45195</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45197</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45197</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45198</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>45198</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55016,7 +55016,7 @@
         <v>45198</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45198</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55140,7 +55140,7 @@
         <v>45201</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45201</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>45202</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>45202</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55368,7 +55368,7 @@
         <v>45203</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55425,7 +55425,7 @@
         <v>45203</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55482,7 +55482,7 @@
         <v>45204</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45204</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45204</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55668,7 +55668,7 @@
         <v>45204</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55730,7 +55730,7 @@
         <v>45204</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>45205</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45205</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>45211</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>45215</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56077,7 +56077,7 @@
         <v>45215</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56139,7 +56139,7 @@
         <v>45216</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45219</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56253,7 +56253,7 @@
         <v>45219</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56310,7 +56310,7 @@
         <v>45219</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56367,7 +56367,7 @@
         <v>45219</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56424,7 +56424,7 @@
         <v>45220</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>45223</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45223</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45223</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56662,7 +56662,7 @@
         <v>45223</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45224</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56781,7 +56781,7 @@
         <v>45225</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>45225</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56895,7 +56895,7 @@
         <v>45225</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56957,7 +56957,7 @@
         <v>45225</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45225</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>45225</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45225</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>45225</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>45225</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         <v>45225</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57376,7 +57376,7 @@
         <v>45226</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57433,7 +57433,7 @@
         <v>45226</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57490,7 +57490,7 @@
         <v>45226</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57547,7 +57547,7 @@
         <v>45226</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57604,7 +57604,7 @@
         <v>45226</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57661,7 +57661,7 @@
         <v>45226</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         <v>45229</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57785,7 +57785,7 @@
         <v>45229</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45229</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57909,7 +57909,7 @@
         <v>45231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45231</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45231</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58090,7 +58090,7 @@
         <v>45231</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58147,7 +58147,7 @@
         <v>45233</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58204,7 +58204,7 @@
         <v>45236</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45236</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>45236</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58380,7 +58380,7 @@
         <v>45237</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>45237</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>45237</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>45237</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58608,7 +58608,7 @@
         <v>45237</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58665,7 +58665,7 @@
         <v>45238</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58722,7 +58722,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45238</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45243</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58950,7 +58950,7 @@
         <v>45243</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59007,7 +59007,7 @@
         <v>45243</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>45243</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45243</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45243</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45244</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45245</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45246</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59634,7 +59634,7 @@
         <v>45247</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>45247</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59758,7 +59758,7 @@
         <v>45247</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59815,7 +59815,7 @@
         <v>45252</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59872,7 +59872,7 @@
         <v>45252</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59929,7 +59929,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59986,7 +59986,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60043,7 +60043,7 @@
         <v>45252</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60100,7 +60100,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60162,7 +60162,7 @@
         <v>45253</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45254</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60286,7 +60286,7 @@
         <v>45257</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60343,7 +60343,7 @@
         <v>45257</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60462,7 +60462,7 @@
         <v>45257</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60524,7 +60524,7 @@
         <v>45260</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>45260</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60695,7 +60695,7 @@
         <v>45264</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60752,7 +60752,7 @@
         <v>45266</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60809,7 +60809,7 @@
         <v>45266</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60866,7 +60866,7 @@
         <v>45266</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60923,7 +60923,7 @@
         <v>45267</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60980,7 +60980,7 @@
         <v>45270</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45271</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61094,7 +61094,7 @@
         <v>45271</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61151,7 +61151,7 @@
         <v>45272</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61208,7 +61208,7 @@
         <v>45273</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61265,7 +61265,7 @@
         <v>45280</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61322,7 +61322,7 @@
         <v>45293</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61379,7 +61379,7 @@
         <v>45294</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61436,7 +61436,7 @@
         <v>45294</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61493,7 +61493,7 @@
         <v>45299</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61550,7 +61550,7 @@
         <v>45301</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61607,7 +61607,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61664,7 +61664,7 @@
         <v>45301</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61721,7 +61721,7 @@
         <v>45301</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61778,7 +61778,7 @@
         <v>45301</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61835,7 +61835,7 @@
         <v>45302</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61897,7 +61897,7 @@
         <v>45302</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>45303</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62016,7 +62016,7 @@
         <v>45308</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62073,7 +62073,7 @@
         <v>45308</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62135,7 +62135,7 @@
         <v>45313</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62192,7 +62192,7 @@
         <v>45314</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62249,7 +62249,7 @@
         <v>45315</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62299,14 +62299,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 3789-2024</t>
+          <t>A 3792-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -62361,14 +62361,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 3794-2024</t>
+          <t>A 3789-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62386,7 +62386,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -62423,14 +62423,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 3792-2024</t>
+          <t>A 3794-2024</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62448,7 +62448,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -62492,7 +62492,7 @@
         <v>45322</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62549,7 +62549,7 @@
         <v>45322</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62606,7 +62606,7 @@
         <v>45324</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62663,7 +62663,7 @@
         <v>45334</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62720,7 +62720,7 @@
         <v>45334</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62777,7 +62777,7 @@
         <v>45336</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62834,7 +62834,7 @@
         <v>45338</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62896,7 +62896,7 @@
         <v>45339</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1026"/>
+  <dimension ref="A1:Z1028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43585</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>43868</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44796</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44313</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>43486</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>43633</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>43788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44920</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>43472</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44311</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44637</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>43788</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>43959</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>43472</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44070</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43398</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>43635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44232</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44523</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>43788</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>43585</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>43859</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44166</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45266</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>43472</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>43502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>43502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>43788</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44676</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45180</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>43509</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>43591</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44501</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44742</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44796</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>43472</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44319</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44634</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44641</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45146</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45308</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>43370</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>43376</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>43484</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>43504</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43543</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43691</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>43788</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>43899</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43942</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43983</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>43987</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44319</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44427</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44464</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44631</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44721</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44790</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45119</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45245</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45246</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45342</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>43318</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43325</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43325</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43327</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43332</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43334</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>43346</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>43347</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43349</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>43369</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>43371</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>43375</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>43375</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43381</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43388</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43389</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43389</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43392</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>43392</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>43392</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>43402</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>43404</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>43409</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>43409</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43409</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>43409</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43412</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>43416</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>43425</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>43425</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>43425</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>43427</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>43427</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43433</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43433</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43434</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43437</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43438</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>43440</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>43443</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>43444</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>43445</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>43448</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>43448</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>43448</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>43448</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>43448</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43448</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>43448</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43448</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>43448</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>43448</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>43451</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>43452</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43453</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43454</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43455</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43472</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>43472</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>43473</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>43476</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>43481</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>43481</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>43482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>43482</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>43484</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>43484</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>43486</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>43486</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43489</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>43489</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>43489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>43489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>43489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>43489</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43489</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43495</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43504</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43522</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43522</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43523</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43523</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43523</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>43529</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43537</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>43538</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>43543</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>43549</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>43549</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>43553</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43558</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43563</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>43565</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>43565</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>43587</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>43590</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>43595</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>43609</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43610</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43610</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43614</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43614</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43614</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43619</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43623</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43631</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>43631</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>43633</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>43634</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>43634</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>43636</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>43643</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>43643</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>43647</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>43654</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>43656</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>43657</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>43675</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>43675</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>43677</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>43683</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>43684</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>43686</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>43686</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>43690</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>43700</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>43700</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>43703</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>43713</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>43713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>43713</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>43713</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43726</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>43733</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>43733</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>43734</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>43735</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>43735</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>43735</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>43749</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>43762</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>43763</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>43782</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>43782</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>43783</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>43787</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>43788</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>43788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>43788</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>43812</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>43819</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>43837</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>43839</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>43859</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>43878</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>43886</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>43888</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>43906</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>43907</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>43907</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>43909</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>43923</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>43924</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>43927</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>43928</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>43930</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>43938</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>43943</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>43945</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43970</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>43979</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43986</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43986</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43986</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43987</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43990</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43990</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43990</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>43990</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>43990</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43991</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43997</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>43998</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>43999</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>43999</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44000</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44005</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44007</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44012</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>44012</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44020</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44021</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44021</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>44043</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44049</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>44056</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>44056</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44056</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44057</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>44061</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44068</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44068</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>44071</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44078</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44084</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44088</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>44090</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>44090</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44096</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44097</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44097</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44105</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44110</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44110</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44131</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44131</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44134</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44137</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44137</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>44137</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44144</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44144</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44146</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44149</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44153</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44154</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>44165</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44165</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44166</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44166</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44166</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44175</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>44182</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>44183</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>44185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>44185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44194</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44200</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44201</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>44203</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44208</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>44210</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44211</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44214</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>44214</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>44214</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>44217</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>44222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44224</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>44229</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>44235</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>44242</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44267</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44267</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44271</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>44277</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44277</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>44286</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>44299</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44300</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44306</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44312</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>44313</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>44313</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>44313</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>44314</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>44315</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44319</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>44321</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44321</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44321</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44325</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44326</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44326</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44328</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44332</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44332</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44333</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44335</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44347</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44348</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44349</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>44350</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44351</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44351</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44354</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44355</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44356</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44356</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44363</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44363</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44363</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44375</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>44375</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>44375</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44379</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>44384</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44385</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>44390</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44390</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44405</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44405</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44405</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44411</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44424</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44424</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44424</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44433</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44435</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>44438</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44438</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44438</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>44440</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>44442</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>44445</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>44445</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44445</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44445</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44447</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44460</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44462</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>44462</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44462</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44468</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44469</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44477</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44489</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44491</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44494</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44495</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44497</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44501</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>44501</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44501</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>44504</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44508</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44508</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>44511</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44512</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44512</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>44512</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44512</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>44512</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>44515</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44516</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44523</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44523</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>44526</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>44529</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44531</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44533</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44537</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44540</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>44540</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>44544</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>44546</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>44547</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>44550</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>44552</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44557</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>44582</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44589</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44603</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>44603</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44610</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>44613</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44616</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44623</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44623</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44631</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44637</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44643</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44644</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44644</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44671</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>44676</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44677</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>44678</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>44686</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44687</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44692</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44692</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44696</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44697</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44701</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44704</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44711</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44712</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44721</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44721</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44721</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44721</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44725</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44725</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>44725</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>44725</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44725</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>44725</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>44733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>44733</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>44734</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>44741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>44741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>44743</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>44743</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>44743</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>44743</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44749</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>44750</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>44756</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44756</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44782</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44789</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44789</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44791</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44795</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44795</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44796</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>44797</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44802</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44802</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44806</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44809</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44809</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44809</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44811</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44811</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>44811</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44811</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44811</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>44811</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>44813</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>44826</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44832</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44832</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44833</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>44833</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44833</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44834</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44834</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44837</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>44840</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>44840</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>44841</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44841</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44844</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44847</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44853</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44853</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44858</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44859</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44860</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>44862</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>44862</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44862</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>44867</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>44867</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44875</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>44882</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44886</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>44888</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>44890</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44893</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44894</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>44896</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>44897</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>44897</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44897</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44900</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>44900</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>44907</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>44908</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>44908</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44916</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44923</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44923</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44923</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44923</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44923</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44928</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44928</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>44928</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>44931</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44936</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>44936</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>44937</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>44938</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44938</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>44938</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>44944</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44946</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>44946</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>44950</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44957</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>44963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>44963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44970</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44978</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>44978</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44978</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>44978</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>44979</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>44981</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>44991</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>44994</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45001</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45002</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45015</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45015</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45019</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45020</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45020</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45027</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45036</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45036</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45036</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45041</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45041</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45041</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45048</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45053</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45053</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45053</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45054</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45054</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45054</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>45054</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45054</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45054</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45056</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45056</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45057</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45057</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45058</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45058</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45061</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45062</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45063</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45063</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45068</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45068</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45071</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45071</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45072</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45072</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45072</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45072</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45072</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45072</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45072</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45075</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45076</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45076</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45077</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45077</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45078</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45078</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45078</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45078</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45079</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45079</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>45079</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45084</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45084</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45084</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45086</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45086</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45089</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45089</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45089</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45089</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45089</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45090</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45090</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45090</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45090</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>45090</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45092</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45092</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>45093</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45093</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45096</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45096</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45097</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45097</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45097</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45099</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45099</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45106</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45106</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45106</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>45106</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45106</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45110</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45114</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45118</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45118</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45119</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45121</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45121</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45128</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45128</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>45128</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50853,7 +50853,7 @@
         <v>45128</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45128</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>45128</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45134</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45139</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45139</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45146</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45149</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45152</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45152</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45153</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51572,7 +51572,7 @@
         <v>45160</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>45162</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45162</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45163</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45163</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45167</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45168</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52177,7 +52177,7 @@
         <v>45168</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45169</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45169</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>45170</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>45170</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45170</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>45173</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45173</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>45173</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>45173</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45173</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45175</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45175</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>45175</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>45175</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>45176</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45187</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45187</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45187</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45187</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45187</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45190</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>45190</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45190</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>45190</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45191</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>45191</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54460,7 +54460,7 @@
         <v>45195</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>45195</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>45195</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>45195</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45197</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45197</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>45198</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45198</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>45198</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45198</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>45201</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>45201</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45202</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45202</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>45203</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>45203</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45204</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45204</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45204</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45204</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45204</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45205</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45205</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45215</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>45215</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>45216</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>45219</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45219</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>45219</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>45219</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45220</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45223</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45223</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45223</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45223</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45224</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45225</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45225</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45225</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45225</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45225</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45225</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45225</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45225</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45225</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45225</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45226</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45226</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57405,7 +57405,7 @@
         <v>45226</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57462,7 +57462,7 @@
         <v>45226</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45226</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45226</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45229</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45229</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45229</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45231</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45231</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45231</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45233</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>45236</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45236</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45236</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45237</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>45237</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>45237</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45237</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45237</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58580,7 +58580,7 @@
         <v>45238</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45238</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58694,7 +58694,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45243</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>45243</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45243</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>45243</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45243</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45243</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>45244</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45246</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>45247</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45247</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45252</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45252</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45252</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45254</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>45257</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>45257</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>45257</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>45260</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45260</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45264</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45266</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45266</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>45266</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60838,7 +60838,7 @@
         <v>45267</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>45270</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45271</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45271</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61066,7 +61066,7 @@
         <v>45272</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45273</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>45280</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>45293</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61294,7 +61294,7 @@
         <v>45294</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>45294</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>45299</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>45301</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>45301</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>45301</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61693,7 +61693,7 @@
         <v>45301</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61750,7 +61750,7 @@
         <v>45302</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>45302</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61874,7 +61874,7 @@
         <v>45303</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61931,7 +61931,7 @@
         <v>45308</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61988,7 +61988,7 @@
         <v>45308</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>45313</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62107,7 +62107,7 @@
         <v>45314</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45315</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62214,14 +62214,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 3792-2024</t>
+          <t>A 3789-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -62276,14 +62276,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 3789-2024</t>
+          <t>A 3794-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -62338,14 +62338,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 3794-2024</t>
+          <t>A 3792-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62363,7 +62363,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -62407,7 +62407,7 @@
         <v>45322</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45322</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45324</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>45334</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>45336</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62749,7 +62749,7 @@
         <v>45338</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62801,7 +62801,7 @@
       </c>
       <c r="R1025" s="2" t="inlineStr"/>
     </row>
-    <row r="1026">
+    <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
           <t>A 6496-2024</t>
@@ -62811,7 +62811,7 @@
         <v>45339</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62857,6 +62857,120 @@
         <v>0</v>
       </c>
       <c r="R1026" s="2" t="inlineStr"/>
+    </row>
+    <row r="1027" ht="15" customHeight="1">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>A 7330-2024</t>
+        </is>
+      </c>
+      <c r="B1027" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C1027" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>MALUNG-SÄLEN</t>
+        </is>
+      </c>
+      <c r="G1027" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1027" s="2" t="inlineStr"/>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>A 7427-2024</t>
+        </is>
+      </c>
+      <c r="B1028" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C1028" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>MALUNG-SÄLEN</t>
+        </is>
+      </c>
+      <c r="G1028" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1028" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43585</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>43868</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44796</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44313</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>43486</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>43633</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>43788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44920</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>43472</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44311</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44637</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>43788</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>43959</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>43472</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44070</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43398</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>43635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44232</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44523</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>43788</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>43585</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>43859</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44166</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45266</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>43472</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>43502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>43502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>43788</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44676</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45180</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>43509</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>43591</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44501</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44742</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44796</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>43472</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44319</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44634</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44641</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45146</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45308</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>43370</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>43376</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>43484</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>43504</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43543</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43691</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>43788</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>43899</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43942</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43983</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>43987</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44319</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44427</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44464</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44631</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44721</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44790</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45119</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45245</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45246</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45342</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>43318</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43325</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43325</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43327</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43332</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43334</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>43346</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>43347</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43349</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>43369</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>43371</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>43375</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>43375</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43381</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43388</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43389</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43389</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43392</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>43392</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>43392</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>43402</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>43404</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>43409</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>43409</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43409</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>43409</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43412</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>43416</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>43425</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>43425</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>43425</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>43427</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>43427</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43433</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43433</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43434</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43437</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43438</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>43440</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>43443</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>43444</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>43445</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>43448</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>43448</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>43448</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>43448</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>43448</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43448</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>43448</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43448</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>43448</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>43448</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>43451</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>43452</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43453</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43454</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43455</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43472</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>43472</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>43473</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>43476</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>43481</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>43481</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>43482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>43482</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>43484</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>43484</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>43486</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>43486</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43489</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>43489</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>43489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>43489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>43489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>43489</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43489</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43495</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43504</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43522</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43522</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43523</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43523</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43523</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>43529</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43537</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>43538</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>43543</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>43549</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>43549</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>43553</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43558</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43563</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>43565</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>43565</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>43587</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>43590</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>43595</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>43609</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43610</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43610</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43614</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43614</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43614</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43619</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43623</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43631</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>43631</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>43633</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>43634</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>43634</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>43636</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>43643</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>43643</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>43647</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>43654</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>43656</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>43657</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>43675</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>43675</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>43677</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>43683</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>43684</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>43686</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>43686</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>43690</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>43700</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>43700</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>43703</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>43713</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>43713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>43713</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>43713</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43726</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>43733</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>43733</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>43734</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>43735</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>43735</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>43735</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>43749</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>43762</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>43763</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>43782</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>43782</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>43783</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>43787</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>43788</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>43788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>43788</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>43812</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>43819</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>43837</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>43839</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>43859</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>43878</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>43886</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>43888</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>43906</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>43907</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>43907</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>43909</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>43923</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>43924</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>43927</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>43928</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>43930</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>43938</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>43943</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>43945</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43970</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>43979</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43986</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43986</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43986</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43987</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43990</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43990</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43990</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>43990</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>43990</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43991</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43997</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>43998</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>43999</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>43999</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44000</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44005</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44007</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44012</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>44012</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44020</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44021</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44021</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>44043</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44049</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>44056</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>44056</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44056</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44057</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>44061</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44068</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44068</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>44071</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44078</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44084</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44088</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>44090</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>44090</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44096</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44097</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44097</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44105</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44110</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44110</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44131</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44131</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44134</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44137</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44137</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>44137</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44144</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44144</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44146</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44149</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44153</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44154</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>44165</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44165</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44166</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44166</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44166</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44175</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>44182</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>44183</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>44185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>44185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44194</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44200</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44201</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>44203</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44208</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>44210</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44211</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44214</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>44214</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>44214</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>44217</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>44222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44224</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>44229</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>44235</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>44242</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44267</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44267</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44271</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>44277</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44277</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>44286</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>44299</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44300</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44306</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44312</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>44313</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>44313</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>44313</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>44314</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>44315</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44319</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>44321</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44321</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44321</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44325</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44326</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44326</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44328</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44332</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44332</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44333</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44335</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44347</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44348</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44349</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>44350</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44351</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44351</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44354</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44355</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44356</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44356</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44363</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44363</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44363</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44375</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>44375</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>44375</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44379</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>44384</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44385</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>44390</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44390</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44405</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44405</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44405</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44411</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44424</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44424</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44424</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44433</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44435</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>44438</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44438</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44438</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>44440</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>44442</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>44445</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>44445</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44445</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44445</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44447</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44460</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44462</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>44462</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44462</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44468</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44469</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44477</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44489</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44491</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44494</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44495</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44497</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44501</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>44501</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44501</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>44504</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44508</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44508</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>44511</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44512</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44512</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>44512</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44512</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>44512</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>44515</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44516</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44523</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44523</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>44526</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>44529</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44531</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44533</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44537</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44540</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>44540</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>44544</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>44546</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>44547</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>44550</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>44552</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44557</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>44582</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44589</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44603</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>44603</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44610</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>44613</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44616</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44623</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44623</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44631</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44637</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44643</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44644</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44644</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44671</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>44676</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44677</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>44678</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>44686</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44687</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44692</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44692</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44696</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44697</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44701</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44704</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44711</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44712</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44721</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44721</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44721</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44721</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44725</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44725</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>44725</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>44725</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44725</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>44725</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>44733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>44733</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>44734</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>44741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>44741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>44743</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>44743</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>44743</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>44743</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44749</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>44750</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>44756</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44756</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44782</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44789</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44789</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44791</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44795</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44795</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44796</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>44797</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44802</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44802</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44806</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44809</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44809</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44809</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44811</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44811</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>44811</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44811</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44811</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>44811</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>44813</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>44826</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44832</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44832</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44833</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>44833</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44833</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44834</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44834</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44837</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>44840</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>44840</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>44841</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44841</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44844</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44847</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44853</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44853</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44858</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44859</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44860</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>44862</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>44862</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44862</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>44867</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>44867</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44875</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>44882</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44886</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>44888</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>44890</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44893</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44894</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>44896</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>44897</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>44897</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44897</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44900</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>44900</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>44907</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>44908</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>44908</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44916</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44923</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44923</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44923</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44923</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44923</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44928</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44928</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>44928</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>44931</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44936</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>44936</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>44937</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>44938</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44938</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>44938</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>44944</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44946</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>44946</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>44950</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44957</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>44963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>44963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44970</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44978</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>44978</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44978</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>44978</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>44979</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>44981</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>44991</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>44994</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45001</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45002</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45015</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45015</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45019</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45020</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45020</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45027</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45036</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45036</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45036</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45041</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45041</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45041</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45048</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45053</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45053</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45053</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45054</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45054</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45054</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>45054</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45054</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45054</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45056</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45056</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45057</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45057</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45058</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45058</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45061</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45062</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45063</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45063</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45068</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45068</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45071</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45071</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45072</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45072</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45072</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45072</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45072</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45072</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45072</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45075</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45076</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45076</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45077</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45077</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45078</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45078</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45078</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45078</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45079</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45079</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>45079</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45084</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45084</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45084</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45086</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45086</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45089</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45089</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45089</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45089</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45089</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45090</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45090</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45090</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45090</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>45090</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45092</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45092</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>45093</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45093</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45096</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45096</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45097</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45097</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45097</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45099</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45099</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45106</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45106</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45106</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>45106</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45106</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45110</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45114</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45118</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45118</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45119</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45121</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45121</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45128</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45128</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>45128</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50853,7 +50853,7 @@
         <v>45128</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45128</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>45128</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45134</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45139</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45139</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45146</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45149</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45152</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45152</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45153</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51572,7 +51572,7 @@
         <v>45160</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>45162</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45162</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45163</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45163</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45167</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45168</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52177,7 +52177,7 @@
         <v>45168</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45169</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45169</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>45170</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>45170</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45170</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>45173</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45173</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>45173</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>45173</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45173</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45175</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45175</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>45175</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>45175</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>45176</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45187</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45187</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45187</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45187</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45187</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45190</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>45190</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45190</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>45190</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45191</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>45191</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54460,7 +54460,7 @@
         <v>45195</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>45195</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>45195</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>45195</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45197</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45197</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>45198</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45198</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>45198</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45198</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>45201</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>45201</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45202</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45202</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>45203</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>45203</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45204</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45204</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45204</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45204</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45204</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45205</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45205</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45215</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>45215</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>45216</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>45219</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45219</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>45219</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>45219</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45220</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45223</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45223</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45223</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45223</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45224</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45225</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45225</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45225</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45225</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45225</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45225</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45225</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45225</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45225</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45225</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45226</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45226</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57405,7 +57405,7 @@
         <v>45226</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57462,7 +57462,7 @@
         <v>45226</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45226</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45226</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45229</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45229</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45229</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45231</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45231</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45231</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45233</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>45236</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45236</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45236</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45237</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>45237</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>45237</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45237</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45237</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58580,7 +58580,7 @@
         <v>45238</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45238</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58694,7 +58694,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45243</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>45243</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45243</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>45243</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45243</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45243</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>45244</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45246</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>45247</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45247</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45252</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45252</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45252</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45254</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>45257</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>45257</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>45257</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>45260</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45260</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45264</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45266</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45266</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>45266</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60838,7 +60838,7 @@
         <v>45267</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>45270</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45271</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45271</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61066,7 +61066,7 @@
         <v>45272</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45273</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>45280</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>45293</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61294,7 +61294,7 @@
         <v>45294</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>45294</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>45299</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>45301</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>45301</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>45301</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61693,7 +61693,7 @@
         <v>45301</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61750,7 +61750,7 @@
         <v>45302</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>45302</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61874,7 +61874,7 @@
         <v>45303</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61931,7 +61931,7 @@
         <v>45308</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61988,7 +61988,7 @@
         <v>45308</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>45313</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62107,7 +62107,7 @@
         <v>45314</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45315</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62214,14 +62214,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 3789-2024</t>
+          <t>A 3792-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -62276,14 +62276,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 3794-2024</t>
+          <t>A 3789-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -62338,14 +62338,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 3792-2024</t>
+          <t>A 3794-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62363,7 +62363,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -62407,7 +62407,7 @@
         <v>45322</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45322</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45324</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>45334</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>45336</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62749,7 +62749,7 @@
         <v>45338</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>45339</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62861,14 +62861,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 7330-2024</t>
+          <t>A 7427-2024</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62881,7 +62881,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -62918,14 +62918,14 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>A 7427-2024</t>
+          <t>A 7330-2024</t>
         </is>
       </c>
       <c r="B1028" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62938,7 +62938,7 @@
         </is>
       </c>
       <c r="G1028" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43585</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>43868</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44796</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44313</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>43486</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>43633</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>43788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44920</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>43472</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44311</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44637</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>43788</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>43959</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>43472</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44070</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43398</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>43635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44232</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44523</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>43788</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>43585</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>43859</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44166</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45266</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>43472</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>43502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>43502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>43788</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44676</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45180</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>43509</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>43591</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44501</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44742</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44796</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>43472</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44319</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44634</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44641</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45146</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45308</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>43370</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>43376</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>43484</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>43504</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43543</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43691</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>43788</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>43899</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43942</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43983</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>43987</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44319</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44427</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44464</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44631</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44721</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44790</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45119</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45245</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45246</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45342</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>43318</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43325</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43325</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43327</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43332</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43334</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>43346</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>43347</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43349</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>43369</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>43371</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>43375</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>43375</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43381</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43388</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43389</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43389</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43392</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>43392</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>43392</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>43402</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>43404</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>43409</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>43409</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43409</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>43409</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43412</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>43416</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>43425</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>43425</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>43425</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>43427</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>43427</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43433</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43433</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43434</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43437</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43438</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>43440</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>43443</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>43444</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>43445</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>43448</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>43448</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>43448</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>43448</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>43448</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43448</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>43448</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43448</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>43448</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>43448</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>43451</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>43452</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43453</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43454</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43455</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43472</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>43472</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>43473</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>43476</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>43481</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>43481</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>43482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>43482</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>43484</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>43484</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>43486</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>43486</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43489</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>43489</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>43489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>43489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>43489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>43489</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43489</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43495</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43504</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43522</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43522</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43523</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43523</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43523</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>43529</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43537</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>43538</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>43543</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>43549</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>43549</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>43553</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43558</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43563</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>43565</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>43565</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>43587</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>43590</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>43595</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>43609</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43610</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43610</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43614</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43614</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43614</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43619</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43623</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43631</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>43631</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>43633</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>43634</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>43634</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>43636</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>43643</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>43643</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>43647</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>43654</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>43656</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>43657</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>43675</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>43675</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>43677</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>43683</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>43684</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>43686</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>43686</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>43690</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>43700</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>43700</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>43703</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>43713</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>43713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>43713</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>43713</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43726</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>43733</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>43733</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>43734</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>43735</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>43735</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>43735</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>43749</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>43762</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>43763</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>43782</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>43782</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>43783</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>43787</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>43788</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>43788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>43788</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>43812</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>43819</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>43837</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>43839</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>43859</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>43878</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>43886</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>43888</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>43906</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>43907</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>43907</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>43909</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>43923</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>43924</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>43927</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>43928</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>43930</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>43938</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>43943</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>43945</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43970</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>43979</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43986</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43986</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43986</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43987</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43990</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43990</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43990</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>43990</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>43990</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43991</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43997</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>43998</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>43999</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>43999</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44000</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44005</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44007</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44012</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>44012</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44020</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44021</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44021</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>44043</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44049</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>44056</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>44056</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44056</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44057</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>44061</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44068</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44068</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>44071</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44078</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44084</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44088</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>44090</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>44090</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44096</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44097</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44097</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44105</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44110</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44110</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44131</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44131</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44134</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44137</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44137</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>44137</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44144</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44144</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44146</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44149</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44153</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44154</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>44165</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44165</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44166</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44166</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44166</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44175</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>44182</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>44183</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>44185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>44185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44194</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44200</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44201</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>44203</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44208</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>44210</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44211</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44214</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>44214</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>44214</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>44217</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>44222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44224</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>44229</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>44235</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>44242</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44267</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44267</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44271</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>44277</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44277</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>44286</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>44299</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44300</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44306</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44312</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>44313</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>44313</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>44313</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>44314</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>44315</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44319</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>44321</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44321</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44321</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44325</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44326</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44326</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44328</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44332</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44332</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44333</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44335</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44347</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44348</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44349</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>44350</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44351</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44351</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44354</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44355</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44356</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44356</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44363</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44363</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44363</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44375</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>44375</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>44375</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44379</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>44384</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44385</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>44390</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44390</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44405</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44405</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44405</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44411</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44424</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44424</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44424</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44433</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44435</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>44438</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44438</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44438</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>44440</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>44442</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>44445</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>44445</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44445</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44445</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44447</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44460</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44462</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>44462</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44462</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44468</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44469</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44477</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44489</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44491</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44494</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44495</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44497</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44501</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>44501</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44501</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>44504</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44508</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44508</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>44511</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44512</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44512</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>44512</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44512</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>44512</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>44515</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44516</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44523</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44523</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>44526</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>44529</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44531</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44533</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44537</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44540</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>44540</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>44544</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>44546</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>44547</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>44550</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>44552</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44557</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>44582</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44589</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44603</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>44603</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44610</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>44613</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44616</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44623</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44623</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44631</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44637</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44643</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44644</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44644</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44671</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>44676</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44677</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>44678</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>44686</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44687</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44692</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44692</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44696</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44697</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44701</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44704</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44711</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44712</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44721</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44721</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44721</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44721</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44725</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44725</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>44725</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>44725</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44725</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>44725</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>44733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>44733</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>44734</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>44741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>44741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>44743</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>44743</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>44743</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>44743</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44749</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>44750</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>44756</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44756</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44782</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44789</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44789</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44791</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44795</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44795</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44796</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>44797</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44802</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44802</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44806</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44809</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44809</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44809</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44811</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44811</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>44811</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44811</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44811</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>44811</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>44813</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>44826</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44832</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44832</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44833</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>44833</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44833</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44834</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44834</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44837</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>44840</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>44840</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>44841</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44841</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44844</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44847</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44853</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44853</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44858</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44859</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44860</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>44862</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>44862</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44862</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>44867</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>44867</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44875</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>44882</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44886</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>44888</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>44890</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44893</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44894</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>44896</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>44897</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>44897</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44897</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44900</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>44900</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>44907</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>44908</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>44908</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44916</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44923</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44923</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44923</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44923</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44923</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44928</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44928</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>44928</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>44931</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44936</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>44936</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>44937</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>44938</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44938</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>44938</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>44944</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44946</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>44946</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>44950</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44957</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>44963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>44963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44970</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44978</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>44978</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44978</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>44978</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>44979</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>44981</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>44991</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>44994</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45001</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45002</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45015</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45015</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45019</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45020</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45020</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45027</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45036</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45036</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45036</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45041</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45041</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45041</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45048</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45053</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45053</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45053</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45054</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45054</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45054</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>45054</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45054</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45054</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45056</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45056</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45057</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45057</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45058</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45058</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45061</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45062</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45063</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45063</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45068</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45068</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45071</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45071</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45072</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45072</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45072</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45072</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45072</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45072</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45072</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45075</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45076</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45076</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45077</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45077</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45078</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45078</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45078</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45078</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45079</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45079</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>45079</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45084</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45084</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45084</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45086</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45086</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45089</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45089</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45089</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45089</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45089</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45090</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45090</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45090</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45090</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>45090</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45092</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45092</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>45093</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45093</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45096</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45096</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45097</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45097</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45097</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45099</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45099</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45106</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45106</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45106</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>45106</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45106</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45110</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45114</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45118</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45118</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45119</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45121</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45121</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45128</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45128</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>45128</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50853,7 +50853,7 @@
         <v>45128</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45128</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>45128</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45134</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45139</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45139</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45146</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45149</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45152</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45152</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45153</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51572,7 +51572,7 @@
         <v>45160</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>45162</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45162</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45163</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45163</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45167</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45168</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52177,7 +52177,7 @@
         <v>45168</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45169</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45169</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>45170</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>45170</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45170</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>45173</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45173</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>45173</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>45173</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45173</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45175</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45175</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>45175</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>45175</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>45176</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45187</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45187</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45187</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45187</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45187</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45190</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>45190</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45190</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>45190</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45191</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>45191</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54460,7 +54460,7 @@
         <v>45195</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>45195</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>45195</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>45195</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45197</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45197</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>45198</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45198</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>45198</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45198</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>45201</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>45201</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45202</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45202</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>45203</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>45203</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45204</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45204</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45204</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45204</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45204</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45205</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45205</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45215</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>45215</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>45216</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>45219</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45219</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>45219</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>45219</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45220</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45223</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45223</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45223</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45223</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45224</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45225</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45225</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45225</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45225</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45225</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45225</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45225</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45225</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45225</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45225</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45226</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45226</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57405,7 +57405,7 @@
         <v>45226</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57462,7 +57462,7 @@
         <v>45226</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45226</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45226</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45229</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45229</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45229</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45231</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45231</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45231</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45233</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>45236</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45236</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45236</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45237</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>45237</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>45237</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45237</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45237</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58580,7 +58580,7 @@
         <v>45238</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45238</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58694,7 +58694,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45243</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>45243</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45243</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>45243</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45243</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45243</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>45244</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45246</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>45247</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45247</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45252</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45252</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45252</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45254</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>45257</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>45257</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>45257</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>45260</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45260</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45264</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45266</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45266</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>45266</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60838,7 +60838,7 @@
         <v>45267</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>45270</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45271</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45271</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61066,7 +61066,7 @@
         <v>45272</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45273</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>45280</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>45293</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61294,7 +61294,7 @@
         <v>45294</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>45294</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>45299</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>45301</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>45301</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>45301</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61693,7 +61693,7 @@
         <v>45301</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61750,7 +61750,7 @@
         <v>45302</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>45302</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61874,7 +61874,7 @@
         <v>45303</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61931,7 +61931,7 @@
         <v>45308</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61988,7 +61988,7 @@
         <v>45308</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>45313</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62107,7 +62107,7 @@
         <v>45314</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45315</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62221,7 +62221,7 @@
         <v>45321</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62283,7 +62283,7 @@
         <v>45321</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62345,7 +62345,7 @@
         <v>45321</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62407,7 +62407,7 @@
         <v>45322</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45322</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45324</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>45334</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>45336</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62749,7 +62749,7 @@
         <v>45338</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>45339</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62868,7 +62868,7 @@
         <v>45345</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>45345</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43585</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>43868</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44796</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44313</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>43486</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>43633</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>43788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44920</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>43472</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44311</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44637</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>43788</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>43959</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>43472</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44070</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43398</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>43635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44232</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44523</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>43788</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>43585</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>43859</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44166</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45266</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>43472</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>43502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>43502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>43788</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44676</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45180</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>43509</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>43591</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44501</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44742</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44796</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>43472</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44319</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44634</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44641</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45146</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45308</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>43370</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>43376</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>43484</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>43504</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43543</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43691</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>43788</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>43899</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43942</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43983</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>43987</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44319</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44427</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44464</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44631</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44721</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44790</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45119</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45245</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45246</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45342</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>43318</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43325</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43325</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43327</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43332</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43334</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>43346</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>43347</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43349</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>43369</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>43371</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>43375</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>43375</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43381</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43388</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43389</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43389</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43392</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>43392</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>43392</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>43402</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>43404</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>43409</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>43409</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43409</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>43409</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43412</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>43416</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>43425</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>43425</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>43425</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>43427</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>43427</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43433</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43433</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43434</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43437</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43438</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>43440</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>43443</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>43444</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>43445</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>43448</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>43448</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>43448</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>43448</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>43448</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43448</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>43448</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43448</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>43448</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>43448</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>43451</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>43452</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43453</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43454</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43455</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43472</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>43472</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>43473</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>43476</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>43481</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>43481</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>43482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>43482</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>43484</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>43484</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>43486</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>43486</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43489</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>43489</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>43489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>43489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>43489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>43489</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43489</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43495</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43504</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43522</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43522</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43523</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43523</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43523</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>43529</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43537</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>43538</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>43543</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>43549</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>43549</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>43553</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43558</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43563</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>43565</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>43565</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>43587</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>43590</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>43595</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>43609</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43610</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43610</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43614</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43614</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43614</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43619</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43623</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43631</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>43631</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>43633</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>43634</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>43634</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>43636</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>43643</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>43643</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>43647</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>43654</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>43656</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>43657</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>43675</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>43675</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>43677</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>43683</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>43684</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>43686</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>43686</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>43690</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>43700</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>43700</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>43703</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>43713</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>43713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>43713</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>43713</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43726</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>43733</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>43733</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>43734</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>43735</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>43735</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>43735</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>43749</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>43762</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>43763</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>43782</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>43782</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>43783</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>43787</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>43788</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>43788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>43788</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>43812</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>43819</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>43837</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>43839</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>43859</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>43878</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>43886</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>43888</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>43906</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>43907</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>43907</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>43909</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>43923</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>43924</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>43927</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>43928</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>43930</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>43938</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>43943</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>43945</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43970</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>43979</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43986</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43986</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43986</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43987</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43990</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43990</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43990</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>43990</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>43990</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43991</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43997</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>43998</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>43999</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>43999</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44000</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44005</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44007</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44012</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>44012</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44020</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44021</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44021</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>44043</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44049</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>44056</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>44056</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44056</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44057</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>44061</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44068</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44068</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>44071</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44078</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44084</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44088</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>44090</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>44090</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44096</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44097</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44097</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44105</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44110</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44110</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44131</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44131</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44134</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44137</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44137</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>44137</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44144</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44144</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44146</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44149</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44153</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44154</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>44165</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44165</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44166</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44166</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44166</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44175</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>44182</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>44183</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>44185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>44185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44194</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44200</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44201</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>44203</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44208</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>44210</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44211</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44214</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>44214</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>44214</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>44217</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>44222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44224</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>44229</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>44235</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>44242</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44267</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44267</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44271</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>44277</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44277</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>44286</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>44299</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44300</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44306</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44312</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>44313</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>44313</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>44313</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>44314</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>44315</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44319</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>44321</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44321</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44321</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44325</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44326</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44326</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44328</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44332</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44332</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44333</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44335</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44347</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44348</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44349</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>44350</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44351</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44351</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44354</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44355</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44356</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44356</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44363</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44363</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44363</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44375</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>44375</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>44375</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44379</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>44384</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44385</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>44390</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44390</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44405</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44405</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44405</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44411</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44424</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44424</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44424</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44433</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44435</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>44438</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44438</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44438</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>44440</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>44442</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>44445</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>44445</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44445</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44445</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44447</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44460</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44462</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>44462</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44462</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44468</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44469</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44477</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44489</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44491</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44494</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44495</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44497</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44501</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>44501</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44501</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>44504</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44508</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44508</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>44511</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44512</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44512</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>44512</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44512</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>44512</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>44515</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44516</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44523</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44523</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>44526</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>44529</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44531</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44533</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44537</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44540</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>44540</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>44544</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>44546</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>44547</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>44550</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>44552</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44557</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>44582</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44589</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44603</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>44603</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44610</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>44613</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44616</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44623</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44623</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44631</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44637</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44643</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44644</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44644</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44671</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>44676</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44677</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>44678</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>44686</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44687</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44692</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44692</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44696</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44697</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44701</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44704</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44711</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44712</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44721</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44721</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44721</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44721</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44725</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44725</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>44725</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>44725</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44725</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>44725</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>44733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>44733</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>44734</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>44741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>44741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>44743</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>44743</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>44743</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>44743</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44749</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>44750</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>44756</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44756</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44782</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44789</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44789</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44791</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44795</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44795</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44796</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>44797</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44802</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44802</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44806</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44809</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44809</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44809</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44811</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44811</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>44811</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44811</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44811</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>44811</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>44813</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>44826</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44832</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44832</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44833</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>44833</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44833</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44834</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44834</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44837</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>44840</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>44840</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>44841</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44841</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44844</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44847</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44853</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44853</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44858</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44859</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44860</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>44862</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>44862</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44862</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>44867</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>44867</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44875</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>44882</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44886</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>44888</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>44890</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44893</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44894</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>44896</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>44897</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>44897</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44897</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44900</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>44900</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>44907</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>44908</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>44908</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44916</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44923</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44923</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44923</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44923</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44923</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44928</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44928</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>44928</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>44931</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44936</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>44936</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>44937</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>44938</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44938</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>44938</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>44944</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44946</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>44946</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>44950</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44957</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>44963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>44963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44970</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44978</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>44978</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44978</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>44978</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>44979</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>44981</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>44991</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>44994</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45001</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45002</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45015</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45015</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45019</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45020</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45020</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45027</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45036</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45036</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45036</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45041</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45041</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45041</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45048</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45053</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45053</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45053</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45054</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45054</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45054</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>45054</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45054</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45054</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45056</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45056</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45057</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45057</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45058</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45058</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45061</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45062</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45063</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45063</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45068</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45068</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45071</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45071</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45072</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45072</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45072</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45072</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45072</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45072</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45072</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45075</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45076</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45076</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45077</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45077</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45078</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45078</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45078</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45078</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45079</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45079</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>45079</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45084</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45084</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45084</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45086</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45086</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45089</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45089</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45089</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45089</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45089</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45090</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45090</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45090</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45090</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>45090</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45092</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45092</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>45093</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45093</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45096</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45096</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45097</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45097</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45097</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45099</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45099</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45106</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45106</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45106</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>45106</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45106</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45110</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45114</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45118</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45118</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45119</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45121</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45121</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45128</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45128</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>45128</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50853,7 +50853,7 @@
         <v>45128</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45128</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>45128</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45134</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45139</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45139</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45146</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45149</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45152</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45152</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45153</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51572,7 +51572,7 @@
         <v>45160</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>45162</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45162</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45163</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45163</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45167</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45168</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52177,7 +52177,7 @@
         <v>45168</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45169</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45169</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>45170</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>45170</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45170</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>45173</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45173</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>45173</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>45173</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45173</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45175</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45175</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>45175</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>45175</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>45176</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45187</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45187</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45187</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45187</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45187</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45190</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>45190</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45190</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>45190</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45191</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>45191</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54460,7 +54460,7 @@
         <v>45195</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>45195</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>45195</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>45195</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45197</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45197</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>45198</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45198</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>45198</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45198</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>45201</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>45201</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45202</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45202</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>45203</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>45203</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45204</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45204</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45204</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45204</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45204</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45205</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45205</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45215</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>45215</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>45216</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>45219</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45219</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>45219</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>45219</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45220</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45223</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45223</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45223</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45223</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45224</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45225</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45225</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45225</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45225</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45225</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45225</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45225</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45225</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45225</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45225</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45226</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45226</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57405,7 +57405,7 @@
         <v>45226</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57462,7 +57462,7 @@
         <v>45226</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45226</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45226</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45229</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45229</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45229</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45231</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45231</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45231</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45233</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>45236</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45236</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45236</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45237</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>45237</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>45237</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45237</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45237</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58580,7 +58580,7 @@
         <v>45238</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45238</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58694,7 +58694,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45243</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>45243</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45243</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>45243</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45243</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45243</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>45244</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45246</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>45247</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45247</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45252</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45252</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45252</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45254</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>45257</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>45257</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>45257</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>45260</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45260</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45264</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45266</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45266</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>45266</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60838,7 +60838,7 @@
         <v>45267</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>45270</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45271</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45271</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61066,7 +61066,7 @@
         <v>45272</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45273</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>45280</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>45293</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61294,7 +61294,7 @@
         <v>45294</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>45294</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>45299</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>45301</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>45301</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>45301</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61693,7 +61693,7 @@
         <v>45301</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61750,7 +61750,7 @@
         <v>45302</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>45302</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61874,7 +61874,7 @@
         <v>45303</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61931,7 +61931,7 @@
         <v>45308</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61988,7 +61988,7 @@
         <v>45308</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>45313</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62107,7 +62107,7 @@
         <v>45314</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45315</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62221,7 +62221,7 @@
         <v>45321</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62283,7 +62283,7 @@
         <v>45321</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62345,7 +62345,7 @@
         <v>45321</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62407,7 +62407,7 @@
         <v>45322</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45322</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45324</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>45334</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>45336</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62749,7 +62749,7 @@
         <v>45338</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>45339</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62861,14 +62861,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 7427-2024</t>
+          <t>A 7330-2024</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62881,7 +62881,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -62918,14 +62918,14 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>A 7330-2024</t>
+          <t>A 7427-2024</t>
         </is>
       </c>
       <c r="B1028" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62938,7 +62938,7 @@
         </is>
       </c>
       <c r="G1028" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43585</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>43868</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44796</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44313</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>43486</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>43633</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>43788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44920</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>43472</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44311</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44637</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>43788</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>43959</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>43472</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44070</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43398</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>43635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44232</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44523</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>43788</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>43585</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>43859</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44166</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45266</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>43472</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>43502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>43502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>43788</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44676</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45180</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>43509</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>43591</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44501</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44742</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44796</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>43472</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44319</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44634</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44641</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45146</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45308</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>43370</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>43376</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>43484</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>43504</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43543</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43691</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>43788</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>43899</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43942</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43983</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>43987</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44319</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44427</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44464</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44631</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44721</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44790</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45119</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45245</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45246</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45342</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>43318</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43325</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43325</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43327</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43332</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43334</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>43346</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>43347</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43349</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>43369</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>43371</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>43375</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>43375</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43381</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43388</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43389</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43389</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43392</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>43392</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>43392</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>43402</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>43404</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>43409</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>43409</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43409</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>43409</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43412</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>43416</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>43425</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>43425</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>43425</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>43427</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>43427</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43433</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43433</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43434</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43437</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43438</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>43440</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>43443</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>43444</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>43445</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>43448</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>43448</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>43448</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>43448</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>43448</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43448</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>43448</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43448</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>43448</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>43448</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>43451</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>43452</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43453</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43454</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43455</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43472</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>43472</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>43473</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>43476</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>43481</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>43481</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>43482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>43482</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>43484</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>43484</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>43486</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>43486</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43489</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>43489</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>43489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>43489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>43489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>43489</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43489</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43495</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43504</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43522</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43522</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43523</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43523</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43523</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>43529</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43537</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>43538</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>43543</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>43549</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>43549</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>43553</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43558</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43563</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>43565</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>43565</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>43587</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>43590</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>43595</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>43609</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43610</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43610</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43614</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43614</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43614</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43619</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43623</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43631</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>43631</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>43633</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>43634</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>43634</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>43636</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>43643</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>43643</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>43647</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>43654</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>43656</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>43657</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>43675</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>43675</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>43677</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>43683</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>43684</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>43686</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>43686</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>43690</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>43700</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>43700</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>43703</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>43713</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>43713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>43713</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>43713</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43726</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>43733</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>43733</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>43734</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>43735</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>43735</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>43735</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>43749</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>43762</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>43763</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>43782</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>43782</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>43783</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>43787</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>43788</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>43788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>43788</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>43812</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>43819</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>43837</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>43839</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>43859</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>43878</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>43886</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>43888</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>43906</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>43907</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>43907</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>43909</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>43923</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>43924</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>43927</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>43928</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>43930</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>43938</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>43943</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>43945</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43970</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>43979</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43986</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43986</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43986</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43987</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43990</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43990</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43990</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>43990</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>43990</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43991</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43997</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>43998</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>43999</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>43999</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44000</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44005</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44007</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44012</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>44012</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44020</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44021</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44021</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>44043</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44049</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>44056</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>44056</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44056</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44057</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>44061</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44068</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44068</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>44071</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44078</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44084</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44088</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>44090</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>44090</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44096</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44097</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44097</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44105</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44110</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44110</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44131</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44131</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44134</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44137</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44137</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>44137</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44144</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44144</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44146</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44149</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44153</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44154</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>44165</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44165</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44166</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44166</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44166</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44175</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>44182</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>44183</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>44185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>44185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44194</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44200</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44201</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>44203</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44208</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>44210</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44211</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44214</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>44214</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>44214</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>44217</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>44222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44224</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>44229</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>44235</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>44242</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44267</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44267</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44271</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>44277</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44277</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>44286</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>44299</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44300</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44306</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44312</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>44313</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>44313</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>44313</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>44314</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>44315</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44319</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>44321</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44321</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44321</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44325</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44326</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44326</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44328</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44332</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44332</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44333</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44335</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44347</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44348</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44349</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>44350</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44351</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44351</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44354</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44355</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44356</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44356</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44363</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44363</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44363</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44375</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>44375</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>44375</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44379</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>44384</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44385</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>44390</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44390</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44405</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44405</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44405</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44411</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44424</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44424</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44424</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44433</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44435</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>44438</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44438</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44438</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>44440</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>44442</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>44445</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>44445</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44445</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44445</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44447</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44460</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44462</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>44462</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44462</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44468</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44469</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44477</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44489</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44491</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44494</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44495</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44497</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44501</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>44501</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44501</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>44504</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44508</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44508</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>44511</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44512</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44512</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>44512</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44512</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>44512</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>44515</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44516</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44523</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44523</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>44526</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>44529</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44531</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44533</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44537</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44540</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>44540</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>44544</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>44546</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>44547</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>44550</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>44552</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44557</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>44582</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44589</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44603</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>44603</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44610</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>44613</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44616</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44623</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44623</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44631</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44637</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44643</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44644</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44644</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44671</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>44676</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44677</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>44678</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>44686</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44687</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44692</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44692</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44696</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44697</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44701</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44704</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44711</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44712</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44721</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44721</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44721</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44721</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44725</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44725</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>44725</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>44725</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44725</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>44725</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>44733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>44733</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>44734</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>44741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>44741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>44743</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>44743</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>44743</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>44743</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44749</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>44750</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>44756</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44756</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44782</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44789</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44789</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44791</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44795</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44795</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44796</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>44797</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44802</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44802</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44806</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44809</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44809</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44809</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44811</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44811</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>44811</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44811</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44811</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>44811</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>44813</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>44826</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44832</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44832</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44833</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>44833</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44833</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44834</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44834</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44837</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>44840</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>44840</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>44841</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44841</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44844</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44847</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44853</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44853</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44858</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44859</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44860</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>44862</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>44862</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44862</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>44867</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>44867</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44875</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>44882</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44886</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>44888</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>44890</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44893</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44894</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>44896</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>44897</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>44897</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44897</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44900</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>44900</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>44907</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>44908</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>44908</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44916</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44923</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44923</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44923</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44923</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44923</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44928</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44928</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>44928</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>44931</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44936</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>44936</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>44937</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>44938</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44938</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>44938</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>44944</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44946</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>44946</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>44950</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44957</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>44963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>44963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44970</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44978</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>44978</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44978</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>44978</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>44979</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>44981</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>44991</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>44994</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45001</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45002</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45015</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45015</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45019</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45020</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45020</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45027</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45036</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45036</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45036</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45041</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45041</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45041</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45048</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45053</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45053</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45053</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45054</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45054</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45054</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>45054</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45054</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45054</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45056</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45056</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45057</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45057</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45058</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45058</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45061</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45062</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45063</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45063</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45068</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45068</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45071</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45071</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45072</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45072</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45072</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45072</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45072</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45072</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45072</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45075</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45076</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45076</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45077</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45077</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45078</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45078</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45078</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45078</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45079</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45079</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>45079</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45084</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45084</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45084</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45086</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45086</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45089</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45089</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45089</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45089</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45089</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45090</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45090</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45090</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45090</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>45090</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45092</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45092</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>45093</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45093</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45096</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45096</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45097</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45097</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45097</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45099</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45099</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45106</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45106</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45106</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>45106</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45106</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45110</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45114</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45118</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45118</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45119</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45121</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45121</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45128</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45128</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>45128</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50853,7 +50853,7 @@
         <v>45128</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45128</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>45128</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45134</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45139</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45139</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45146</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45149</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45152</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45152</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45153</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51572,7 +51572,7 @@
         <v>45160</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>45162</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45162</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45163</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45163</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45167</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45168</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52177,7 +52177,7 @@
         <v>45168</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45169</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45169</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>45170</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>45170</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45170</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>45173</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45173</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>45173</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>45173</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45173</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45175</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45175</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>45175</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>45175</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>45176</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45187</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45187</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45187</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45187</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45187</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45190</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>45190</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45190</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>45190</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45191</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>45191</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54460,7 +54460,7 @@
         <v>45195</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>45195</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>45195</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>45195</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45197</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45197</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>45198</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45198</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>45198</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45198</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>45201</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>45201</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45202</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45202</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>45203</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>45203</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45204</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45204</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45204</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45204</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45204</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45205</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45205</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45215</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>45215</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>45216</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>45219</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45219</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>45219</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>45219</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45220</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45223</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45223</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45223</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45223</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45224</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45225</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45225</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45225</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45225</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45225</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45225</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45225</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45225</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45225</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45225</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45226</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45226</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57405,7 +57405,7 @@
         <v>45226</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57462,7 +57462,7 @@
         <v>45226</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45226</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45226</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45229</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45229</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45229</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45231</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45231</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45231</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45233</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>45236</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45236</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45236</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45237</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>45237</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>45237</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45237</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45237</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58580,7 +58580,7 @@
         <v>45238</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45238</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58694,7 +58694,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45243</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>45243</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45243</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>45243</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45243</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45243</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>45244</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45246</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>45247</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45247</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45252</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45252</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45252</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45254</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>45257</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>45257</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>45257</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>45260</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45260</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45264</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45266</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45266</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>45266</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60838,7 +60838,7 @@
         <v>45267</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>45270</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45271</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45271</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61066,7 +61066,7 @@
         <v>45272</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45273</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>45280</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>45293</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61294,7 +61294,7 @@
         <v>45294</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>45294</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>45299</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>45301</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>45301</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>45301</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61693,7 +61693,7 @@
         <v>45301</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61750,7 +61750,7 @@
         <v>45302</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>45302</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61874,7 +61874,7 @@
         <v>45303</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61931,7 +61931,7 @@
         <v>45308</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61988,7 +61988,7 @@
         <v>45308</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>45313</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62107,7 +62107,7 @@
         <v>45314</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45315</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62214,14 +62214,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 3792-2024</t>
+          <t>A 3789-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -62276,14 +62276,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 3789-2024</t>
+          <t>A 3794-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -62338,14 +62338,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 3794-2024</t>
+          <t>A 3792-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62363,7 +62363,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -62407,7 +62407,7 @@
         <v>45322</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45322</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45324</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>45334</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>45336</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62749,7 +62749,7 @@
         <v>45338</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>45339</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62868,7 +62868,7 @@
         <v>45345</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>45345</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43585</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>43868</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44796</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44313</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>43486</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>43633</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>43788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44920</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>43472</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44311</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44637</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>43788</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>43959</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>43472</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44070</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43398</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>43635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44232</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44523</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>43788</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>43585</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>43859</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44166</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45266</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>43472</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>43502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>43502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>43788</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44676</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45180</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>43509</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>43591</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44501</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44742</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44796</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>43472</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44319</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44634</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44641</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45146</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45308</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>43370</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>43376</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>43484</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>43504</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43543</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43691</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>43788</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>43899</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43942</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43983</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>43987</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44319</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44427</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44464</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44631</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44721</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44790</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45119</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45245</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45246</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45342</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>43318</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43325</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43325</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43327</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43332</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43334</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>43346</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>43347</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43349</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>43369</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>43371</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>43375</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>43375</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43381</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43388</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43389</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43389</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43392</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>43392</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>43392</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>43402</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>43404</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>43409</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>43409</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43409</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>43409</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43412</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>43416</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>43425</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>43425</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>43425</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>43427</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>43427</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43433</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43433</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43434</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43437</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43438</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>43440</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>43443</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>43444</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>43445</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>43448</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>43448</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>43448</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>43448</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>43448</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43448</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>43448</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43448</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>43448</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>43448</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>43451</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>43452</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43453</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43454</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43455</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43472</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>43472</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>43473</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>43476</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>43481</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>43481</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>43482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>43482</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>43484</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>43484</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>43486</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>43486</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43489</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>43489</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>43489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>43489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>43489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>43489</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43489</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43495</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43504</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43522</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43522</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43523</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43523</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43523</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>43529</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43537</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>43538</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>43543</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>43549</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>43549</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>43553</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43558</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43563</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>43565</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>43565</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>43587</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>43590</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>43595</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>43609</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43610</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43610</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43614</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43614</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43614</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43619</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43623</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43631</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>43631</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>43633</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>43634</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>43634</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>43636</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>43643</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>43643</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>43647</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>43654</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>43656</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>43657</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>43675</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>43675</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>43677</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>43683</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>43684</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>43686</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>43686</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>43690</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>43700</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>43700</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>43703</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>43713</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>43713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>43713</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>43713</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43726</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>43733</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>43733</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>43734</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>43735</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>43735</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>43735</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>43749</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>43762</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>43763</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>43782</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>43782</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>43783</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>43787</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>43788</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>43788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>43788</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>43812</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>43819</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>43837</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>43839</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>43859</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>43878</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>43886</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>43888</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>43906</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>43907</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>43907</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>43909</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>43923</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>43924</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>43927</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>43928</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>43930</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>43938</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>43943</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>43945</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43970</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>43979</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43986</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43986</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43986</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43987</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43990</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43990</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43990</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>43990</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>43990</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43991</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43997</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>43998</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>43999</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>43999</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44000</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44005</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44007</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44012</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>44012</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44020</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44021</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44021</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>44043</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44049</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>44056</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>44056</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44056</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44057</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>44061</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44068</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44068</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>44071</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44078</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44084</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44088</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>44090</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>44090</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44096</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44097</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44097</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44105</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44110</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44110</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44131</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44131</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44134</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44137</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44137</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>44137</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44144</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44144</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44146</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44149</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44153</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44154</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>44165</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44165</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44166</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44166</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44166</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44175</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>44182</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>44183</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>44185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>44185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44194</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44200</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44201</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>44203</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44208</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>44210</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44211</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44214</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>44214</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>44214</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>44217</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>44222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44224</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>44229</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>44235</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>44242</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44267</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44267</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44271</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>44277</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44277</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>44286</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>44299</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44300</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44306</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44312</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>44313</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>44313</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>44313</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>44314</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>44315</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44319</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>44321</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44321</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44321</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44325</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44326</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44326</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44328</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44332</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44332</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44333</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44335</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44347</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44348</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44349</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>44350</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44351</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44351</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44354</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44355</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44356</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44356</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44363</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44363</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44363</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44375</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>44375</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>44375</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44379</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>44384</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44385</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>44390</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44390</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44405</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44405</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44405</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44411</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44424</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44424</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44424</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44433</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44435</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>44438</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44438</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44438</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>44440</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>44442</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>44445</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>44445</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44445</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44445</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44447</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44460</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44462</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>44462</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44462</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44468</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44469</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44477</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44489</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44491</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44494</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44495</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44497</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44501</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>44501</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44501</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>44504</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44508</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44508</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>44511</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44512</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44512</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>44512</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44512</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>44512</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>44515</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44516</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44523</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44523</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>44526</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>44529</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44531</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44533</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44537</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44540</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>44540</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>44544</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>44546</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>44547</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>44550</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>44552</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44557</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>44582</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44589</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44603</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>44603</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44610</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>44613</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44616</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44623</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44623</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44631</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44637</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44643</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44644</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44644</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44671</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>44676</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44677</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>44678</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>44686</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44687</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44692</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44692</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44696</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44697</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44701</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44704</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44711</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44712</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44721</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44721</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44721</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44721</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44725</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44725</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>44725</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>44725</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44725</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>44725</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>44733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>44733</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>44734</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>44741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>44741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>44743</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>44743</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>44743</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>44743</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44749</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>44750</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>44756</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44756</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44782</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44789</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44789</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44791</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44795</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44795</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44796</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>44797</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44802</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44802</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44806</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44809</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44809</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44809</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44811</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44811</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>44811</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44811</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44811</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>44811</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>44813</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>44826</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44832</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44832</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44833</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>44833</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44833</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44834</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44834</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44837</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>44840</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>44840</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>44841</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44841</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44844</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44847</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44853</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44853</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44858</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44859</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44860</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>44862</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>44862</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44862</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>44867</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>44867</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44875</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>44882</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44886</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>44888</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>44890</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44893</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44894</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>44896</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>44897</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>44897</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44897</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44900</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>44900</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>44907</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>44908</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>44908</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44916</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44923</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44923</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44923</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44923</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44923</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44928</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44928</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>44928</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>44931</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44936</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>44936</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>44937</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>44938</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44938</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>44938</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>44944</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44946</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>44946</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>44950</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44957</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>44963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>44963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44970</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44978</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>44978</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44978</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>44978</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>44979</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>44981</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>44991</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>44994</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45001</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45002</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45015</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45015</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45019</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45020</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45020</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45027</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45036</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45036</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45036</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45041</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45041</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45041</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45048</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45053</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45053</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45053</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45054</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45054</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45054</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>45054</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45054</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45054</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45056</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45056</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45057</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45057</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45058</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45058</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45061</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45062</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45063</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45063</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45068</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45068</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45071</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45071</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45072</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45072</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45072</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45072</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45072</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45072</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45072</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45075</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45076</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45076</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45077</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45077</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45078</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45078</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45078</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45078</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45079</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45079</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>45079</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45084</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45084</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45084</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45086</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45086</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45089</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45089</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45089</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45089</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45089</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45090</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45090</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45090</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45090</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>45090</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45092</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45092</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>45093</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45093</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45096</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45096</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45097</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45097</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45097</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45099</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45099</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45106</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45106</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45106</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>45106</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45106</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45110</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45114</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45118</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45118</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45119</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45121</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45121</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45128</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45128</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>45128</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50853,7 +50853,7 @@
         <v>45128</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45128</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>45128</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45134</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45139</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45139</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45146</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45149</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45152</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45152</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45153</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51572,7 +51572,7 @@
         <v>45160</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>45162</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45162</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45163</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45163</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45167</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45168</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52177,7 +52177,7 @@
         <v>45168</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45169</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45169</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>45170</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>45170</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45170</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>45173</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45173</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>45173</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>45173</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45173</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45175</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45175</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>45175</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>45175</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>45176</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45187</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45187</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45187</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45187</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45187</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45190</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>45190</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45190</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>45190</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45191</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>45191</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54460,7 +54460,7 @@
         <v>45195</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>45195</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>45195</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>45195</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45197</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45197</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>45198</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45198</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>45198</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45198</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>45201</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>45201</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45202</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45202</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>45203</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>45203</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45204</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45204</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45204</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45204</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45204</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45205</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45205</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45215</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>45215</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>45216</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>45219</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45219</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>45219</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>45219</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45220</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45223</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45223</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45223</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45223</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45224</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45225</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45225</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45225</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45225</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45225</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45225</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45225</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45225</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45225</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45225</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45226</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45226</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57405,7 +57405,7 @@
         <v>45226</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57462,7 +57462,7 @@
         <v>45226</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45226</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45226</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45229</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45229</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45229</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45231</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45231</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45231</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45233</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>45236</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45236</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45236</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45237</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>45237</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>45237</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45237</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45237</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58580,7 +58580,7 @@
         <v>45238</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45238</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58694,7 +58694,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45243</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>45243</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45243</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>45243</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45243</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45243</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>45244</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45246</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>45247</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45247</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45252</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45252</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45252</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45254</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>45257</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>45257</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>45257</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>45260</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45260</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45264</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45266</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45266</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>45266</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60838,7 +60838,7 @@
         <v>45267</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>45270</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45271</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45271</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61066,7 +61066,7 @@
         <v>45272</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>45273</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>45280</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>45293</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61294,7 +61294,7 @@
         <v>45294</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>45294</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>45299</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>45301</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>45301</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>45301</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61693,7 +61693,7 @@
         <v>45301</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -61750,7 +61750,7 @@
         <v>45302</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>45302</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -61874,7 +61874,7 @@
         <v>45303</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61931,7 +61931,7 @@
         <v>45308</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61988,7 +61988,7 @@
         <v>45308</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>45313</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62107,7 +62107,7 @@
         <v>45314</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45315</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62221,7 +62221,7 @@
         <v>45321</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62283,7 +62283,7 @@
         <v>45321</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62345,7 +62345,7 @@
         <v>45321</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62407,7 +62407,7 @@
         <v>45322</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45322</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45324</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>45334</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>45336</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -62749,7 +62749,7 @@
         <v>45338</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>45339</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -62868,7 +62868,7 @@
         <v>45345</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>45345</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -569,7 +569,7 @@
         <v>43585</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>43868</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>44796</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44313</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>43486</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>43633</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>43788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44920</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>43472</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>44311</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44637</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>43788</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>43959</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>43472</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44070</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>43398</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>43635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>44232</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44523</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>43788</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>43585</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>43859</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44166</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45099</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45266</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>43472</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>43502</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>43502</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>43788</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44363</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44676</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45180</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>43509</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>43591</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44501</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44742</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>44796</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>43472</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44319</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44634</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44641</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>44741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45146</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>45308</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>43370</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>43376</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>43484</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>43504</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43543</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43691</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>43788</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>43899</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43942</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43983</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>43987</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44319</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44427</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44464</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44631</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44721</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44790</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45119</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45245</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45246</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45342</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>43318</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43325</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43325</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>43327</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>43332</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>43334</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>43346</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>43347</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>43349</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>43369</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>43371</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>43375</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>43375</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43381</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43388</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43389</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43389</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43392</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>43392</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>43392</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>43402</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>43404</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>43409</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>43409</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43409</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>43409</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43412</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>43416</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>43425</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>43425</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>43425</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>43426</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>43427</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>43427</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43431</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43431</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43431</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43431</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43433</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43433</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43434</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43437</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43438</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>43440</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>43443</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>43444</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>43445</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>43448</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>43448</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>43448</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>43448</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>43448</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43448</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>43448</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43448</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>43448</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>43448</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>43451</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>43452</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>43453</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>43454</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>43455</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>43472</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>43472</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>43473</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>43476</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>43481</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>43481</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>43482</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>43482</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>43484</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>43484</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>43486</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>43486</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43489</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>43489</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>43489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>43489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>43489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>43489</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43489</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>43495</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>43504</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>43522</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>43522</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>43523</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>43523</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>43523</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>43529</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>43537</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>43538</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>43543</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>43549</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>43549</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>43553</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43558</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43563</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>43565</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>43565</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>43587</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>43590</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>43595</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>43609</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43610</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43610</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43614</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43614</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43614</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43619</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43623</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43631</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>43631</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>43633</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>43634</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>43634</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>43636</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>43643</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>43643</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>43647</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>43654</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>43656</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>43657</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>43675</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>43675</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>43677</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>43683</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>43684</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>43686</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>43686</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>43690</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>43700</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>43700</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>43703</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>43713</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>43713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>43713</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>43713</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43726</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>43733</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>43733</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>43734</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>43735</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>43735</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>43735</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>43749</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>43762</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>43763</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>43782</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>43782</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>43783</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>43787</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>43788</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>43788</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>43788</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>43812</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>43819</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>43837</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>43839</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>43859</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>43878</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>43886</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>43888</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>43906</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>43907</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>43907</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>43909</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>43923</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>43924</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>43927</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>43928</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>43930</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>43938</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>43943</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>43945</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>43970</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>43979</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>43986</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         <v>43986</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>43986</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>43987</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>43990</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>43990</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>43990</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>43990</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>43990</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>43991</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>43997</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>43998</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>43999</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>43999</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44000</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44005</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44007</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44012</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>44012</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44020</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44021</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44021</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>44043</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44049</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>44056</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>44056</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44056</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44057</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>44061</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44068</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44068</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>44071</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44078</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44084</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44088</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>44090</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>44090</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44096</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44097</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44097</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>44103</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44105</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>44110</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44110</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44111</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44131</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44131</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44134</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44137</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44137</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>44137</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44144</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44144</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44146</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44149</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44153</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44154</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>44165</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44165</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44166</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44166</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44166</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44175</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>44182</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>44183</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>44185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>44185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44194</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44200</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44201</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>44203</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44208</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>44210</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44211</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44214</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>44214</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>44214</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>44217</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>44222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44224</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>44229</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>44235</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>44242</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44267</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44267</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>44271</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>44277</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44277</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>44286</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>44299</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44300</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44306</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44312</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>44313</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>44313</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>44313</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>44314</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>44315</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44319</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>44321</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44321</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44321</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44325</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44326</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44326</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44328</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44332</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44332</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44333</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44335</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44347</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44348</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44349</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>44350</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44351</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44351</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44354</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44355</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44356</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44356</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44363</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44363</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44363</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44375</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>44375</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>44375</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44379</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>44384</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44385</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>44390</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44390</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44405</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44405</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44405</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>44411</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44424</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44424</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44424</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44433</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>44435</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>44438</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44438</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44438</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>44439</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>44440</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>44440</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>44442</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>44445</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>44445</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44445</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44445</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44447</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44460</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44462</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>44462</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44462</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44468</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44469</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44477</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44489</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44491</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44494</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44495</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44497</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>44501</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>44501</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44501</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>44504</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44508</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44508</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>44511</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>44511</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44512</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44512</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>44512</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44512</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>44512</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>44515</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>44515</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44515</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44515</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44516</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44523</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44523</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>44526</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>44529</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44531</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44533</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44537</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44540</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>44540</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>44544</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>44546</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>44547</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>44550</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>44552</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44557</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>44582</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44589</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44603</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>44603</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44610</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>44613</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44616</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44623</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44623</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44631</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44637</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44643</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44644</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44644</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44671</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>44676</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44677</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>44678</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>44686</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44687</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44692</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44692</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44696</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44697</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44701</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44704</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44711</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44712</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44721</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44721</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44721</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44721</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44725</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44725</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>44725</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>44725</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44725</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>44725</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>44726</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>44733</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>44733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>44733</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>44734</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>44739</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>44741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>44741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>44741</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>44743</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>44743</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>44743</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>44743</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44749</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>44750</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>44756</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44756</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44782</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44789</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44789</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44791</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44795</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44795</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44796</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>44797</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44802</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44802</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44804</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44806</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44809</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44809</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44809</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44809</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44810</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44811</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44811</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>44811</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44811</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44811</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>44811</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>44813</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44819</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>44826</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44832</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44832</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44833</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>44833</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44833</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44834</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>44834</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44837</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>44840</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>44840</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>44841</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44841</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44841</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44844</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44847</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44853</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44853</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44855</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44858</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44859</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44860</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>44862</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>44862</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>44862</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44862</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44862</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>44865</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>44867</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>44867</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44875</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44881</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>44881</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44881</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>44881</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>44882</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44886</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44886</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>44886</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44887</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>44887</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>44888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>44888</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>44890</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44893</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>44893</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44894</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>44896</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>44897</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>44897</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44897</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44900</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>44900</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44900</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>44907</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>44908</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>44908</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>44908</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44911</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44916</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44923</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44923</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44923</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44923</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44923</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44928</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44928</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>44928</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>44931</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44936</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>44936</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>44937</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>44938</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44938</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>44938</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>44944</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>44946</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>44946</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>44950</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44957</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>44963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>44963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44970</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44978</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>44978</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44978</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>44978</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>44979</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>44981</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>44991</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>44994</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45001</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45002</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45015</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45015</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45019</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45020</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45020</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45027</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45036</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45036</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45036</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45041</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45041</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45041</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45048</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45053</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45053</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45053</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45054</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45054</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45054</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>45054</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45054</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45054</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45056</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45056</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45057</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45057</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45058</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45058</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45061</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45062</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45063</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45063</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45068</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45068</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45071</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45071</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45072</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45072</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45072</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45072</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45072</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45072</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45072</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45072</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45075</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45076</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45076</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45077</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45077</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45078</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45078</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45078</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45078</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45079</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45079</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>45079</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45084</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45084</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45084</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45086</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45086</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45089</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45089</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45089</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45089</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45089</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45090</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45090</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45090</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45090</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45090</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>45090</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45092</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45092</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>45093</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45093</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45096</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45096</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45097</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45097</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45097</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45099</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45099</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45106</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45106</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45106</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>45106</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45106</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45110</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45114</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45118</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45118</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45119</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45121</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45121</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45128</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45128</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>45128</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50853,7 +50853,7 @@
         <v>45128</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45128</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>45128</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45134</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45139</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45139</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45146</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45149</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45152</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45152</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45153</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51572,7 +51572,7 @@
         <v>45160</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>45162</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45162</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45163</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45163</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45167</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45168</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52177,7 +52177,7 @@
         <v>45168</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45169</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45169</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>45170</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>45170</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45170</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>45173</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45173</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>45173</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>45173</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45173</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45175</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45175</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>45175</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>45175</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>45176</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>45187</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45187</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45187</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45187</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45187</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45190</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>45190</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45190</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>45190</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45191</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>45191</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54460,7 +54460,7 @@
         <v>45195</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>45195</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>45195</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>45195</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45197</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45197</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>45198</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45198</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>45198</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45198</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>45201</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>45201</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45202</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45202</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>45203</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>45203</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>45204</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45204</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45204</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45204</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45204</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45205</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55821,7 +55821,7 @@
         <v>45205</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45215</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>45215</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>45216</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>45219</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45219</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>45219</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>45219</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45220</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45223</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45223</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45223</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45223</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45224</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>45225</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>45225</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56810,7 +56810,7 @@
         <v>45225</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45225</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45225</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45225</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45225</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45225</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45225</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45225</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45226</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45226</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57405,7 +57405,7 @@
         <v>45226</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57462,7 +57462,7 @@
         <v>45226</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45226</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45226</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45229</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45229</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45229</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45231</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45231</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45231</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45233</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>45236</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45236</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45236</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45237</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>45237</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>45237</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45237</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45237</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58580,7 +58580,7 @@
         <v>45238</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45238</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58694,7 +58694,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45243</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>45243</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45243</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>45243</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45243</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45243</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>45244</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45246</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>45247</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45247</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45252</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45252</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45252</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45254</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>45257</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>45257</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>45257</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60439,7 +60439,7 @@
         <v>45260</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60496,7 +60496,7 @@
         <v>45260</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45264</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45266</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45266</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r=